--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T412"/>
+  <dimension ref="A1:T413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27620,6 +27620,72 @@
         <v>311.31</v>
       </c>
       <c r="T412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>263.97</v>
+      </c>
+      <c r="C413" t="n">
+        <v>264.55</v>
+      </c>
+      <c r="D413" t="n">
+        <v>251.47</v>
+      </c>
+      <c r="E413" t="n">
+        <v>251</v>
+      </c>
+      <c r="F413" t="n">
+        <v>260.71</v>
+      </c>
+      <c r="G413" t="n">
+        <v>263.42</v>
+      </c>
+      <c r="H413" t="n">
+        <v>257.24</v>
+      </c>
+      <c r="I413" t="n">
+        <v>252.91</v>
+      </c>
+      <c r="J413" t="n">
+        <v>267.37</v>
+      </c>
+      <c r="K413" t="n">
+        <v>285.66</v>
+      </c>
+      <c r="L413" t="n">
+        <v>314.18</v>
+      </c>
+      <c r="M413" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="N413" t="n">
+        <v>293.85</v>
+      </c>
+      <c r="O413" t="n">
+        <v>302.84</v>
+      </c>
+      <c r="P413" t="n">
+        <v>305.75</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>300.58</v>
+      </c>
+      <c r="R413" t="n">
+        <v>311.15</v>
+      </c>
+      <c r="S413" t="n">
+        <v>311.95</v>
+      </c>
+      <c r="T413" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27636,7 +27702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31769,6 +31835,16 @@
       </c>
       <c r="B413" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -31937,28 +32013,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3290979509938927</v>
+        <v>-0.3382485439895506</v>
       </c>
       <c r="J2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04828999398473821</v>
+        <v>0.05086818138701799</v>
       </c>
       <c r="M2" t="n">
-        <v>8.482167451635977</v>
+        <v>8.505137248475048</v>
       </c>
       <c r="N2" t="n">
-        <v>115.8461089510162</v>
+        <v>116.2955289576489</v>
       </c>
       <c r="O2" t="n">
-        <v>10.76318303063811</v>
+        <v>10.78404047459248</v>
       </c>
       <c r="P2" t="n">
-        <v>290.0213234684832</v>
+        <v>290.112925581903</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32015,28 +32091,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4109524278615115</v>
+        <v>-0.4089177288691235</v>
       </c>
       <c r="J3" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1017826704997704</v>
+        <v>0.1014015738294848</v>
       </c>
       <c r="M3" t="n">
-        <v>7.081853085081791</v>
+        <v>7.074091742215329</v>
       </c>
       <c r="N3" t="n">
-        <v>80.88617523830462</v>
+        <v>80.72418391013778</v>
       </c>
       <c r="O3" t="n">
-        <v>8.993674179016306</v>
+        <v>8.984663817313244</v>
       </c>
       <c r="P3" t="n">
-        <v>271.5222777721394</v>
+        <v>271.5019093951431</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32093,28 +32169,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2500417632115378</v>
+        <v>-0.2511872683498542</v>
       </c>
       <c r="J4" t="n">
+        <v>412</v>
+      </c>
+      <c r="K4" t="n">
         <v>411</v>
       </c>
-      <c r="K4" t="n">
-        <v>410</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04919309973936803</v>
+        <v>0.04990800231675752</v>
       </c>
       <c r="M4" t="n">
-        <v>6.644306604617382</v>
+        <v>6.63358134228129</v>
       </c>
       <c r="N4" t="n">
-        <v>65.20970211513779</v>
+        <v>65.06244412464717</v>
       </c>
       <c r="O4" t="n">
-        <v>8.075252449003548</v>
+        <v>8.066129438872599</v>
       </c>
       <c r="P4" t="n">
-        <v>260.2364339807588</v>
+        <v>260.2479160648679</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32171,28 +32247,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2779852006044924</v>
+        <v>-0.2802289087112328</v>
       </c>
       <c r="J5" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K5" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05936749972438093</v>
+        <v>0.06058547685756832</v>
       </c>
       <c r="M5" t="n">
-        <v>6.641002873925505</v>
+        <v>6.635296815111287</v>
       </c>
       <c r="N5" t="n">
-        <v>66.54525409794485</v>
+        <v>66.42795396470405</v>
       </c>
       <c r="O5" t="n">
-        <v>8.157527450027052</v>
+        <v>8.150334592193381</v>
       </c>
       <c r="P5" t="n">
-        <v>262.6218344495737</v>
+        <v>262.6442021204854</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32249,28 +32325,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1529388562371265</v>
+        <v>-0.152215804319202</v>
       </c>
       <c r="J6" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K6" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02122204053186472</v>
+        <v>0.02115205249122487</v>
       </c>
       <c r="M6" t="n">
-        <v>6.114193311754813</v>
+        <v>6.102366419394179</v>
       </c>
       <c r="N6" t="n">
-        <v>59.04237573895067</v>
+        <v>58.90264959209669</v>
       </c>
       <c r="O6" t="n">
-        <v>7.683903678401407</v>
+        <v>7.67480615990376</v>
       </c>
       <c r="P6" t="n">
-        <v>263.3583303530775</v>
+        <v>263.3511403289441</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32327,28 +32403,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0150407826082922</v>
+        <v>-0.0141878782638719</v>
       </c>
       <c r="J7" t="n">
+        <v>412</v>
+      </c>
+      <c r="K7" t="n">
         <v>411</v>
       </c>
-      <c r="K7" t="n">
-        <v>410</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0001968973729494783</v>
+        <v>0.0001762730559737857</v>
       </c>
       <c r="M7" t="n">
-        <v>6.439117621223141</v>
+        <v>6.427476663534807</v>
       </c>
       <c r="N7" t="n">
-        <v>62.57770919568213</v>
+        <v>62.43185982596442</v>
       </c>
       <c r="O7" t="n">
-        <v>7.91060738475132</v>
+        <v>7.901383412160457</v>
       </c>
       <c r="P7" t="n">
-        <v>262.1830343323418</v>
+        <v>262.1745386013369</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32405,28 +32481,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02220965720059625</v>
+        <v>0.02264668847334199</v>
       </c>
       <c r="J8" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K8" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006283464657855786</v>
+        <v>0.0006573312784252661</v>
       </c>
       <c r="M8" t="n">
-        <v>5.324587810587544</v>
+        <v>5.313681541531746</v>
       </c>
       <c r="N8" t="n">
-        <v>42.6396936994559</v>
+        <v>42.53787688887277</v>
       </c>
       <c r="O8" t="n">
-        <v>6.529907633302013</v>
+        <v>6.522106783001393</v>
       </c>
       <c r="P8" t="n">
-        <v>255.8207813867856</v>
+        <v>255.8164245938243</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32483,28 +32559,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06765367133465593</v>
+        <v>0.06795706370249448</v>
       </c>
       <c r="J9" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K9" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008744412063317886</v>
+        <v>0.00887638084115927</v>
       </c>
       <c r="M9" t="n">
-        <v>4.411560121722756</v>
+        <v>4.402501330429163</v>
       </c>
       <c r="N9" t="n">
-        <v>28.19942725864159</v>
+        <v>28.13179052914764</v>
       </c>
       <c r="O9" t="n">
-        <v>5.310313291948186</v>
+        <v>5.303941037487845</v>
       </c>
       <c r="P9" t="n">
-        <v>250.551269421908</v>
+        <v>250.5482448838139</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32561,28 +32637,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08035676823917141</v>
+        <v>0.08129211546649477</v>
       </c>
       <c r="J10" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K10" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01417060787622615</v>
+        <v>0.01458180766918404</v>
       </c>
       <c r="M10" t="n">
-        <v>4.027300756753745</v>
+        <v>4.021803379290995</v>
       </c>
       <c r="N10" t="n">
-        <v>24.41522446363333</v>
+        <v>24.36364855657353</v>
       </c>
       <c r="O10" t="n">
-        <v>4.941176425066538</v>
+        <v>4.935954675295705</v>
       </c>
       <c r="P10" t="n">
-        <v>263.4664142159876</v>
+        <v>263.4570896791167</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32639,28 +32715,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.002983024916769645</v>
+        <v>-0.001318843597205503</v>
       </c>
       <c r="J11" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K11" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L11" t="n">
-        <v>2.085024400211299e-05</v>
+        <v>4.096570746403572e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>3.651573447698131</v>
+        <v>3.648981309921686</v>
       </c>
       <c r="N11" t="n">
-        <v>23.30261659023355</v>
+        <v>23.27024689978017</v>
       </c>
       <c r="O11" t="n">
-        <v>4.82727838333709</v>
+        <v>4.823924429318951</v>
       </c>
       <c r="P11" t="n">
-        <v>282.5567920431572</v>
+        <v>282.5402289805709</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32717,28 +32793,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01018901137681395</v>
+        <v>-0.008915937570483741</v>
       </c>
       <c r="J12" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K12" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002152189940910487</v>
+        <v>0.0001657390347219456</v>
       </c>
       <c r="M12" t="n">
-        <v>3.91404100122431</v>
+        <v>3.909805705399032</v>
       </c>
       <c r="N12" t="n">
-        <v>26.21153977600565</v>
+        <v>26.16215489132249</v>
       </c>
       <c r="O12" t="n">
-        <v>5.119720673631097</v>
+        <v>5.114895393976547</v>
       </c>
       <c r="P12" t="n">
-        <v>312.0114618208819</v>
+        <v>311.99877046595</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32795,28 +32871,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09863339927588002</v>
+        <v>-0.09598672167170309</v>
       </c>
       <c r="J13" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K13" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0209081090816543</v>
+        <v>0.01989513373650675</v>
       </c>
       <c r="M13" t="n">
-        <v>3.828107678267147</v>
+        <v>3.829304705038158</v>
       </c>
       <c r="N13" t="n">
-        <v>24.76048876944785</v>
+        <v>24.76191714977588</v>
       </c>
       <c r="O13" t="n">
-        <v>4.975991234864452</v>
+        <v>4.976134760009607</v>
       </c>
       <c r="P13" t="n">
-        <v>301.8905300025063</v>
+        <v>301.8641451026694</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32873,28 +32949,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1846196162212112</v>
+        <v>-0.1843429575737746</v>
       </c>
       <c r="J14" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K14" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08628768836023681</v>
+        <v>0.0865370221878462</v>
       </c>
       <c r="M14" t="n">
-        <v>3.600236287645088</v>
+        <v>3.592614102920494</v>
       </c>
       <c r="N14" t="n">
-        <v>19.61637907345153</v>
+        <v>19.56943878214227</v>
       </c>
       <c r="O14" t="n">
-        <v>4.429038165725322</v>
+        <v>4.42373584000472</v>
       </c>
       <c r="P14" t="n">
-        <v>298.1878160081858</v>
+        <v>298.1850579802756</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32951,28 +33027,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3196684892543226</v>
+        <v>-0.318573480308709</v>
       </c>
       <c r="J15" t="n">
+        <v>412</v>
+      </c>
+      <c r="K15" t="n">
         <v>411</v>
       </c>
-      <c r="K15" t="n">
-        <v>410</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2489838995309186</v>
+        <v>0.2487400293671119</v>
       </c>
       <c r="M15" t="n">
-        <v>3.203068056272505</v>
+        <v>3.199410255449895</v>
       </c>
       <c r="N15" t="n">
-        <v>16.79120539758208</v>
+        <v>16.76091287150503</v>
       </c>
       <c r="O15" t="n">
-        <v>4.09770733430074</v>
+        <v>4.094009388302014</v>
       </c>
       <c r="P15" t="n">
-        <v>309.1814658241166</v>
+        <v>309.1705585031364</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33029,28 +33105,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4105430936678801</v>
+        <v>-0.410179375962364</v>
       </c>
       <c r="J16" t="n">
+        <v>412</v>
+      </c>
+      <c r="K16" t="n">
         <v>411</v>
       </c>
-      <c r="K16" t="n">
-        <v>410</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.3529865163020159</v>
+        <v>0.3539797950493545</v>
       </c>
       <c r="M16" t="n">
-        <v>3.262426295129048</v>
+        <v>3.256092256682898</v>
       </c>
       <c r="N16" t="n">
-        <v>16.82972231840574</v>
+        <v>16.78993939290681</v>
       </c>
       <c r="O16" t="n">
-        <v>4.102404455731509</v>
+        <v>4.097552854193196</v>
       </c>
       <c r="P16" t="n">
-        <v>315.8802664894788</v>
+        <v>315.8766435183825</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33107,28 +33183,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3946980876796793</v>
+        <v>-0.3947070086019834</v>
       </c>
       <c r="J17" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K17" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3193206793420515</v>
+        <v>0.3206778795774307</v>
       </c>
       <c r="M17" t="n">
-        <v>3.438205781374605</v>
+        <v>3.42990721939457</v>
       </c>
       <c r="N17" t="n">
-        <v>18.04878917416903</v>
+        <v>18.00498213246074</v>
       </c>
       <c r="O17" t="n">
-        <v>4.248386655445691</v>
+        <v>4.243227796437606</v>
       </c>
       <c r="P17" t="n">
-        <v>311.0045073806207</v>
+        <v>311.0045963138708</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33185,28 +33261,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3169000189308175</v>
+        <v>-0.3162238700480856</v>
       </c>
       <c r="J18" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K18" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2686612249866804</v>
+        <v>0.2689854014918028</v>
       </c>
       <c r="M18" t="n">
-        <v>2.939172577822123</v>
+        <v>2.935218750005549</v>
       </c>
       <c r="N18" t="n">
-        <v>14.85801029689235</v>
+        <v>14.82596272291172</v>
       </c>
       <c r="O18" t="n">
-        <v>3.854608968091621</v>
+        <v>3.85044967801317</v>
       </c>
       <c r="P18" t="n">
-        <v>318.2107235787635</v>
+        <v>318.2039830069169</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33263,28 +33339,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2611059958137648</v>
+        <v>-0.2617782123005236</v>
       </c>
       <c r="J19" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K19" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2488270853895682</v>
+        <v>0.2508848001244594</v>
       </c>
       <c r="M19" t="n">
-        <v>2.614150583174453</v>
+        <v>2.610967083233904</v>
       </c>
       <c r="N19" t="n">
-        <v>11.18609419851012</v>
+        <v>11.16291247011996</v>
       </c>
       <c r="O19" t="n">
-        <v>3.344561884389361</v>
+        <v>3.341094501824209</v>
       </c>
       <c r="P19" t="n">
-        <v>320.1229034079486</v>
+        <v>320.129604777486</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33322,7 +33398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T412"/>
+  <dimension ref="A1:T413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75281,6 +75357,108 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-38.528222168839896,178.28900036625882</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-38.52863876254042,178.2882771848419</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-38.528958795374336,178.28745745147094</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-38.52936796181297,178.28672684838784</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-38.52984908595098,178.2860681998457</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-38.53031555812878,178.28530433553743</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-38.530851901108534,178.284489422875</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-38.53145783048307,178.28385555828945</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-38.532097073646256,178.2834608799658</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-38.53275560802057,178.28310250099966</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-38.533538740931306,178.2827852011453</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-38.534299235340434,178.28247473407816</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-38.53498380689499,178.28220458393704</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-38.53568015161802,178.2821580704813</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-38.536361762429465,178.2820181130085</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-38.53703516627665,178.2817676603572</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>-38.53773825587932,178.28169319761906</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>-38.53842569955426,178.28150871309947</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T413"/>
+  <dimension ref="A1:T414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27500,7 +27500,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>273.91</v>
+        <v>280.25</v>
       </c>
       <c r="C411" t="n">
         <v>265.99</v>
@@ -27566,7 +27566,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>270.8</v>
+        <v>281.08</v>
       </c>
       <c r="C412" t="n">
         <v>265.24</v>
@@ -27632,7 +27632,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>263.97</v>
+        <v>279.95</v>
       </c>
       <c r="C413" t="n">
         <v>264.55</v>
@@ -27688,6 +27688,72 @@
       <c r="T413" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:54:11+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>283.52</v>
+      </c>
+      <c r="C414" t="n">
+        <v>267.87</v>
+      </c>
+      <c r="D414" t="n">
+        <v>261.72</v>
+      </c>
+      <c r="E414" t="n">
+        <v>262.01</v>
+      </c>
+      <c r="F414" t="n">
+        <v>265.96</v>
+      </c>
+      <c r="G414" t="n">
+        <v>269.67</v>
+      </c>
+      <c r="H414" t="n">
+        <v>263.25</v>
+      </c>
+      <c r="I414" t="n">
+        <v>255.39</v>
+      </c>
+      <c r="J414" t="n">
+        <v>269.84</v>
+      </c>
+      <c r="K414" t="n">
+        <v>287.81</v>
+      </c>
+      <c r="L414" t="n">
+        <v>317.34</v>
+      </c>
+      <c r="M414" t="n">
+        <v>306.7</v>
+      </c>
+      <c r="N414" t="n">
+        <v>299.01</v>
+      </c>
+      <c r="O414" t="n">
+        <v>303.12</v>
+      </c>
+      <c r="P414" t="n">
+        <v>307.01</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>302.76</v>
+      </c>
+      <c r="R414" t="n">
+        <v>314.12</v>
+      </c>
+      <c r="S414" t="n">
+        <v>314.09</v>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27702,7 +27768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B414"/>
+  <dimension ref="A1:B415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31845,6 +31911,16 @@
       </c>
       <c r="B414" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -32013,28 +32089,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3382485439895506</v>
+        <v>-0.3200521488175493</v>
       </c>
       <c r="J2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05086818138701799</v>
+        <v>0.04649071036669017</v>
       </c>
       <c r="M2" t="n">
-        <v>8.505137248475048</v>
+        <v>8.408135910341985</v>
       </c>
       <c r="N2" t="n">
-        <v>116.2955289576489</v>
+        <v>114.8844240633853</v>
       </c>
       <c r="O2" t="n">
-        <v>10.78404047459248</v>
+        <v>10.71841518431644</v>
       </c>
       <c r="P2" t="n">
-        <v>290.112925581903</v>
+        <v>289.9310204221577</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32091,28 +32167,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4089177288691235</v>
+        <v>-0.4051248686086767</v>
       </c>
       <c r="J3" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1014015738294848</v>
+        <v>0.1001377386083393</v>
       </c>
       <c r="M3" t="n">
-        <v>7.074091742215329</v>
+        <v>7.074579952532294</v>
       </c>
       <c r="N3" t="n">
-        <v>80.72418391013778</v>
+        <v>80.652340634563</v>
       </c>
       <c r="O3" t="n">
-        <v>8.984663817313244</v>
+        <v>8.980664821412889</v>
       </c>
       <c r="P3" t="n">
-        <v>271.5019093951431</v>
+        <v>271.4637773575025</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32169,28 +32245,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2511872683498542</v>
+        <v>-0.2469073832635267</v>
       </c>
       <c r="J4" t="n">
+        <v>413</v>
+      </c>
+      <c r="K4" t="n">
         <v>412</v>
       </c>
-      <c r="K4" t="n">
-        <v>411</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04990800231675752</v>
+        <v>0.04847912215044714</v>
       </c>
       <c r="M4" t="n">
-        <v>6.63358134228129</v>
+        <v>6.636549310472973</v>
       </c>
       <c r="N4" t="n">
-        <v>65.06244412464717</v>
+        <v>65.06312285547429</v>
       </c>
       <c r="O4" t="n">
-        <v>8.066129438872599</v>
+        <v>8.066171511657453</v>
       </c>
       <c r="P4" t="n">
-        <v>260.2479160648679</v>
+        <v>260.2048333740494</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32247,28 +32323,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2802289087112328</v>
+        <v>-0.2766720259516575</v>
       </c>
       <c r="J5" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K5" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06058547685756832</v>
+        <v>0.05940240806562891</v>
       </c>
       <c r="M5" t="n">
-        <v>6.635296815111287</v>
+        <v>6.63557885635921</v>
       </c>
       <c r="N5" t="n">
-        <v>66.42795396470405</v>
+        <v>66.37782637505109</v>
       </c>
       <c r="O5" t="n">
-        <v>8.150334592193381</v>
+        <v>8.147258825829157</v>
       </c>
       <c r="P5" t="n">
-        <v>262.6442021204854</v>
+        <v>262.608591206272</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32325,28 +32401,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.152215804319202</v>
+        <v>-0.1487415777568265</v>
       </c>
       <c r="J6" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K6" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02115205249122487</v>
+        <v>0.02030447110855638</v>
       </c>
       <c r="M6" t="n">
-        <v>6.102366419394179</v>
+        <v>6.102340316159548</v>
       </c>
       <c r="N6" t="n">
-        <v>58.90264959209669</v>
+        <v>58.86552585167399</v>
       </c>
       <c r="O6" t="n">
-        <v>7.67480615990376</v>
+        <v>7.672387232906978</v>
       </c>
       <c r="P6" t="n">
-        <v>263.3511403289441</v>
+        <v>263.3164427139168</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32403,28 +32479,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0141878782638719</v>
+        <v>-0.01006640590416116</v>
       </c>
       <c r="J7" t="n">
+        <v>413</v>
+      </c>
+      <c r="K7" t="n">
         <v>412</v>
       </c>
-      <c r="K7" t="n">
-        <v>411</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0001762730559737857</v>
+        <v>8.908553016551135e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>6.427476663534807</v>
+        <v>6.431100701001102</v>
       </c>
       <c r="N7" t="n">
-        <v>62.43185982596442</v>
+        <v>62.42940554930698</v>
       </c>
       <c r="O7" t="n">
-        <v>7.901383412160457</v>
+        <v>7.901228103865056</v>
       </c>
       <c r="P7" t="n">
-        <v>262.1745386013369</v>
+        <v>262.1333080549288</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32481,28 +32557,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02264668847334199</v>
+        <v>0.02622477325156627</v>
       </c>
       <c r="J8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006573312784252661</v>
+        <v>0.0008844307115370986</v>
       </c>
       <c r="M8" t="n">
-        <v>5.313681541531746</v>
+        <v>5.317556278936418</v>
       </c>
       <c r="N8" t="n">
-        <v>42.53787688887277</v>
+        <v>42.54691836442039</v>
       </c>
       <c r="O8" t="n">
-        <v>6.522106783001393</v>
+        <v>6.522799886890628</v>
       </c>
       <c r="P8" t="n">
-        <v>255.8164245938243</v>
+        <v>255.7806014085527</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32559,28 +32635,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06795706370249448</v>
+        <v>0.06955124854895663</v>
       </c>
       <c r="J9" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K9" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00887638084115927</v>
+        <v>0.009344086076749081</v>
       </c>
       <c r="M9" t="n">
-        <v>4.402501330429163</v>
+        <v>4.400466208466239</v>
       </c>
       <c r="N9" t="n">
-        <v>28.13179052914764</v>
+        <v>28.08591530500084</v>
       </c>
       <c r="O9" t="n">
-        <v>5.303941037487845</v>
+        <v>5.299614637405331</v>
       </c>
       <c r="P9" t="n">
-        <v>250.5482448838139</v>
+        <v>250.5322841722457</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32637,28 +32713,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08129211546649477</v>
+        <v>0.08350851487502199</v>
       </c>
       <c r="J10" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K10" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01458180766918404</v>
+        <v>0.01544322563231648</v>
       </c>
       <c r="M10" t="n">
-        <v>4.021803379290995</v>
+        <v>4.022078841585339</v>
       </c>
       <c r="N10" t="n">
-        <v>24.36364855657353</v>
+        <v>24.34764623906005</v>
       </c>
       <c r="O10" t="n">
-        <v>4.935954675295705</v>
+        <v>4.934333413852376</v>
       </c>
       <c r="P10" t="n">
-        <v>263.4570896791167</v>
+        <v>263.4348994596086</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32715,28 +32791,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.001318843597205503</v>
+        <v>0.001460409521546004</v>
       </c>
       <c r="J11" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K11" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L11" t="n">
-        <v>4.096570746403572e-06</v>
+        <v>5.039864815814532e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>3.648981309921686</v>
+        <v>3.650539337304915</v>
       </c>
       <c r="N11" t="n">
-        <v>23.27024689978017</v>
+        <v>23.28161379159813</v>
       </c>
       <c r="O11" t="n">
-        <v>4.823924429318951</v>
+        <v>4.82510246436261</v>
       </c>
       <c r="P11" t="n">
-        <v>282.5402289805709</v>
+        <v>282.5124483863473</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32793,28 +32869,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.008915937570483741</v>
+        <v>-0.005993407381409852</v>
       </c>
       <c r="J12" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K12" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001657390347219456</v>
+        <v>7.515276745229116e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.909805705399032</v>
+        <v>3.912274077361457</v>
       </c>
       <c r="N12" t="n">
-        <v>26.16215489132249</v>
+        <v>26.17355376698224</v>
       </c>
       <c r="O12" t="n">
-        <v>5.114895393976547</v>
+        <v>5.116009555012797</v>
       </c>
       <c r="P12" t="n">
-        <v>311.99877046595</v>
+        <v>311.9695105833831</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32871,28 +32947,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09598672167170309</v>
+        <v>-0.09212505353369889</v>
       </c>
       <c r="J13" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K13" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01989513373650675</v>
+        <v>0.01837278599437486</v>
       </c>
       <c r="M13" t="n">
-        <v>3.829304705038158</v>
+        <v>3.835528890826677</v>
       </c>
       <c r="N13" t="n">
-        <v>24.76191714977588</v>
+        <v>24.83246286062823</v>
       </c>
       <c r="O13" t="n">
-        <v>4.976134760009607</v>
+        <v>4.983218122923001</v>
       </c>
       <c r="P13" t="n">
-        <v>301.8641451026694</v>
+        <v>301.8254827283156</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32949,28 +33025,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1843429575737746</v>
+        <v>-0.1813550545882852</v>
       </c>
       <c r="J14" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K14" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0865370221878462</v>
+        <v>0.08416103316605095</v>
       </c>
       <c r="M14" t="n">
-        <v>3.592614102920494</v>
+        <v>3.596122869452754</v>
       </c>
       <c r="N14" t="n">
-        <v>19.56943878214227</v>
+        <v>19.60018194843302</v>
       </c>
       <c r="O14" t="n">
-        <v>4.42373584000472</v>
+        <v>4.427209273168936</v>
       </c>
       <c r="P14" t="n">
-        <v>298.1850579802756</v>
+        <v>298.1551435962246</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33027,28 +33103,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.318573480308709</v>
+        <v>-0.3173229363611771</v>
       </c>
       <c r="J15" t="n">
+        <v>413</v>
+      </c>
+      <c r="K15" t="n">
         <v>412</v>
       </c>
-      <c r="K15" t="n">
-        <v>411</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2487400293671119</v>
+        <v>0.2482820875684012</v>
       </c>
       <c r="M15" t="n">
-        <v>3.199410255449895</v>
+        <v>3.196328067570966</v>
       </c>
       <c r="N15" t="n">
-        <v>16.76091287150503</v>
+        <v>16.73395599077902</v>
       </c>
       <c r="O15" t="n">
-        <v>4.094009388302014</v>
+        <v>4.090715828651389</v>
       </c>
       <c r="P15" t="n">
-        <v>309.1705585031364</v>
+        <v>309.1580482626777</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33105,28 +33181,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.410179375962364</v>
+        <v>-0.4091324598256253</v>
       </c>
       <c r="J16" t="n">
+        <v>413</v>
+      </c>
+      <c r="K16" t="n">
         <v>412</v>
       </c>
-      <c r="K16" t="n">
-        <v>411</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.3539797950493545</v>
+        <v>0.3541054424602873</v>
       </c>
       <c r="M16" t="n">
-        <v>3.256092256682898</v>
+        <v>3.252753746097333</v>
       </c>
       <c r="N16" t="n">
-        <v>16.78993939290681</v>
+        <v>16.75880625923479</v>
       </c>
       <c r="O16" t="n">
-        <v>4.097552854193196</v>
+        <v>4.093752100364015</v>
       </c>
       <c r="P16" t="n">
-        <v>315.8766435183825</v>
+        <v>315.8661703377825</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33183,28 +33259,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3947070086019834</v>
+        <v>-0.3935486537364791</v>
       </c>
       <c r="J17" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K17" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3206778795774307</v>
+        <v>0.3206140009962857</v>
       </c>
       <c r="M17" t="n">
-        <v>3.42990721939457</v>
+        <v>3.426238814172058</v>
       </c>
       <c r="N17" t="n">
-        <v>18.00498213246074</v>
+        <v>17.97312875589529</v>
       </c>
       <c r="O17" t="n">
-        <v>4.243227796437606</v>
+        <v>4.239472697859404</v>
       </c>
       <c r="P17" t="n">
-        <v>311.0045963138708</v>
+        <v>310.9929990590462</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33261,28 +33337,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3162238700480856</v>
+        <v>-0.3139794124057295</v>
       </c>
       <c r="J18" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K18" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2689854014918028</v>
+        <v>0.2668310992784523</v>
       </c>
       <c r="M18" t="n">
-        <v>2.935218750005549</v>
+        <v>2.938651970592546</v>
       </c>
       <c r="N18" t="n">
-        <v>14.82596272291172</v>
+        <v>14.83414940741191</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85044967801317</v>
+        <v>3.85151261291092</v>
       </c>
       <c r="P18" t="n">
-        <v>318.2039830069169</v>
+        <v>318.181511873073</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33339,28 +33415,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2617782123005236</v>
+        <v>-0.2613093301788146</v>
       </c>
       <c r="J19" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2508848001244594</v>
+        <v>0.2513512031279963</v>
       </c>
       <c r="M19" t="n">
-        <v>2.610967083233904</v>
+        <v>2.606763594274438</v>
       </c>
       <c r="N19" t="n">
-        <v>11.16291247011996</v>
+        <v>11.13780757898775</v>
       </c>
       <c r="O19" t="n">
-        <v>3.341094501824209</v>
+        <v>3.337335401032949</v>
       </c>
       <c r="P19" t="n">
-        <v>320.129604777486</v>
+        <v>320.1249104082472</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33398,7 +33474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T413"/>
+  <dimension ref="A1:T414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75161,7 +75237,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>-38.528292431105406,178.28907062452103</t>
+          <t>-38.52833724624523,178.2891154372083</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -75263,7 +75339,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>-38.528270447645696,178.28904864229312</t>
+          <t>-38.528343113209914,178.2891213038577</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -75365,7 +75441,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>-38.528222168839896,178.28900036625882</t>
+          <t>-38.5283351256555,178.28911331673285</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -75456,6 +75532,108 @@
       <c r="T413" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:54:11+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-38.52836036067019,178.28913855039897</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-38.52866223052925,178.2883006513792</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-38.529031249630926,178.2875299007551</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-38.52944578863497,178.28680466954611</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-38.52988619697968,178.2861053080908</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-38.53035732096781,178.28535217114592</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-38.53088596119469,178.28454280423617</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-38.531470324358416,178.28387906117408</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-38.53210951717779,178.28348428827172</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-38.532766439458015,178.2831228768269</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-38.533549050211484,178.28281889688225</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-38.53430215124778,178.28250136930376</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-38.534989814509174,178.2822631365515</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-38.535680513822726,178.28216124142293</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-38.536363667303114,178.28203232707298</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-38.53703865593536,178.28179220977702</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>-38.53774301012157,178.2817266437222</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-38.53842912518269,178.28153281254384</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T414"/>
+  <dimension ref="A1:T416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27754,6 +27754,138 @@
       <c r="T414" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>288.32</v>
+      </c>
+      <c r="C415" t="n">
+        <v>269.44</v>
+      </c>
+      <c r="D415" t="n">
+        <v>264.21</v>
+      </c>
+      <c r="E415" t="n">
+        <v>263.15</v>
+      </c>
+      <c r="F415" t="n">
+        <v>267.33</v>
+      </c>
+      <c r="G415" t="n">
+        <v>270.53</v>
+      </c>
+      <c r="H415" t="n">
+        <v>263.79</v>
+      </c>
+      <c r="I415" t="n">
+        <v>255.97</v>
+      </c>
+      <c r="J415" t="n">
+        <v>269.13</v>
+      </c>
+      <c r="K415" t="n">
+        <v>288.23</v>
+      </c>
+      <c r="L415" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="M415" t="n">
+        <v>306.59</v>
+      </c>
+      <c r="N415" t="n">
+        <v>300.53</v>
+      </c>
+      <c r="O415" t="n">
+        <v>309.97</v>
+      </c>
+      <c r="P415" t="n">
+        <v>312.61</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>303.09</v>
+      </c>
+      <c r="R415" t="n">
+        <v>315.27</v>
+      </c>
+      <c r="S415" t="n">
+        <v>314.28</v>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>286.07</v>
+      </c>
+      <c r="C416" t="n">
+        <v>267.66</v>
+      </c>
+      <c r="D416" t="n">
+        <v>262.63</v>
+      </c>
+      <c r="E416" t="n">
+        <v>262.43</v>
+      </c>
+      <c r="F416" t="n">
+        <v>266.84</v>
+      </c>
+      <c r="G416" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="H416" t="n">
+        <v>263.47</v>
+      </c>
+      <c r="I416" t="n">
+        <v>255.91</v>
+      </c>
+      <c r="J416" t="n">
+        <v>268.65</v>
+      </c>
+      <c r="K416" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="L416" t="n">
+        <v>315.93</v>
+      </c>
+      <c r="M416" t="n">
+        <v>306.17</v>
+      </c>
+      <c r="N416" t="n">
+        <v>300.02</v>
+      </c>
+      <c r="O416" t="n">
+        <v>309.97</v>
+      </c>
+      <c r="P416" t="n">
+        <v>312.61</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>303.91</v>
+      </c>
+      <c r="R416" t="n">
+        <v>314.59</v>
+      </c>
+      <c r="S416" t="n">
+        <v>314.82</v>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27768,7 +27900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B415"/>
+  <dimension ref="A1:B417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31921,6 +32053,26 @@
       </c>
       <c r="B415" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -32089,28 +32241,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3200521488175493</v>
+        <v>-0.3140306415661454</v>
       </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K2" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04649071036669017</v>
+        <v>0.0453100530821996</v>
       </c>
       <c r="M2" t="n">
-        <v>8.408135910341985</v>
+        <v>8.394507329582645</v>
       </c>
       <c r="N2" t="n">
-        <v>114.8844240633853</v>
+        <v>114.4907791464184</v>
       </c>
       <c r="O2" t="n">
-        <v>10.71841518431644</v>
+        <v>10.7000364086492</v>
       </c>
       <c r="P2" t="n">
-        <v>289.9310204221577</v>
+        <v>289.8702863838548</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32167,28 +32319,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4051248686086767</v>
+        <v>-0.3969389020491227</v>
       </c>
       <c r="J3" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K3" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1001377386083393</v>
+        <v>0.09728543770419551</v>
       </c>
       <c r="M3" t="n">
-        <v>7.074579952532294</v>
+        <v>7.078505278875324</v>
       </c>
       <c r="N3" t="n">
-        <v>80.652340634563</v>
+        <v>80.55798950261389</v>
       </c>
       <c r="O3" t="n">
-        <v>8.980664821412889</v>
+        <v>8.975410269319942</v>
       </c>
       <c r="P3" t="n">
-        <v>271.4637773575025</v>
+        <v>271.3812064100805</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32245,28 +32397,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2469073832635267</v>
+        <v>-0.2367050350475273</v>
       </c>
       <c r="J4" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K4" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04847912215044714</v>
+        <v>0.04496537392486233</v>
       </c>
       <c r="M4" t="n">
-        <v>6.636549310472973</v>
+        <v>6.649791530892129</v>
       </c>
       <c r="N4" t="n">
-        <v>65.06312285547429</v>
+        <v>65.20540812393442</v>
       </c>
       <c r="O4" t="n">
-        <v>8.066171511657453</v>
+        <v>8.074986571130284</v>
       </c>
       <c r="P4" t="n">
-        <v>260.2048333740494</v>
+        <v>260.1017943665768</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32323,28 +32475,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2766720259516575</v>
+        <v>-0.268858372084804</v>
       </c>
       <c r="J5" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K5" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05940240806562891</v>
+        <v>0.05672756479735519</v>
       </c>
       <c r="M5" t="n">
-        <v>6.63557885635921</v>
+        <v>6.639653359512329</v>
       </c>
       <c r="N5" t="n">
-        <v>66.37782637505109</v>
+        <v>66.32744634739625</v>
       </c>
       <c r="O5" t="n">
-        <v>8.147258825829157</v>
+        <v>8.14416639978557</v>
       </c>
       <c r="P5" t="n">
-        <v>262.608591206272</v>
+        <v>262.5301001665248</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32401,28 +32553,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1487415777568265</v>
+        <v>-0.1407418296428923</v>
       </c>
       <c r="J6" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02030447110855638</v>
+        <v>0.01835404616118452</v>
       </c>
       <c r="M6" t="n">
-        <v>6.102340316159548</v>
+        <v>6.10672497537668</v>
       </c>
       <c r="N6" t="n">
-        <v>58.86552585167399</v>
+        <v>58.86432906455335</v>
       </c>
       <c r="O6" t="n">
-        <v>7.672387232906978</v>
+        <v>7.672309239372026</v>
       </c>
       <c r="P6" t="n">
-        <v>263.3164427139168</v>
+        <v>263.2362762463209</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32479,28 +32631,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01006640590416116</v>
+        <v>-0.001407328818127536</v>
       </c>
       <c r="J7" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K7" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L7" t="n">
-        <v>8.908553016551135e-05</v>
+        <v>1.753801713633152e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>6.431100701001102</v>
+        <v>6.440208078853118</v>
       </c>
       <c r="N7" t="n">
-        <v>62.42940554930698</v>
+        <v>62.45946722708535</v>
       </c>
       <c r="O7" t="n">
-        <v>7.901228103865056</v>
+        <v>7.903130217014354</v>
       </c>
       <c r="P7" t="n">
-        <v>262.1333080549288</v>
+        <v>262.0463920602051</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32557,28 +32709,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02622477325156627</v>
+        <v>0.03363978061357423</v>
       </c>
       <c r="J8" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K8" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008844307115370986</v>
+        <v>0.001464283687964585</v>
       </c>
       <c r="M8" t="n">
-        <v>5.317556278936418</v>
+        <v>5.326998588881999</v>
       </c>
       <c r="N8" t="n">
-        <v>42.54691836442039</v>
+        <v>42.58413535730306</v>
       </c>
       <c r="O8" t="n">
-        <v>6.522799886890628</v>
+        <v>6.525652102074019</v>
       </c>
       <c r="P8" t="n">
-        <v>255.7806014085527</v>
+        <v>255.7061133305474</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32635,28 +32787,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06955124854895663</v>
+        <v>0.07324300453587379</v>
       </c>
       <c r="J9" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K9" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009344086076749081</v>
+        <v>0.01045797327196074</v>
       </c>
       <c r="M9" t="n">
-        <v>4.400466208466239</v>
+        <v>4.399103382469713</v>
       </c>
       <c r="N9" t="n">
-        <v>28.08591530500084</v>
+        <v>28.0105840085846</v>
       </c>
       <c r="O9" t="n">
-        <v>5.299614637405331</v>
+        <v>5.292502622444754</v>
       </c>
       <c r="P9" t="n">
-        <v>250.5322841722457</v>
+        <v>250.4951978752711</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32713,28 +32865,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08350851487502199</v>
+        <v>0.08686577007052289</v>
       </c>
       <c r="J10" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K10" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01544322563231648</v>
+        <v>0.0168601980703208</v>
       </c>
       <c r="M10" t="n">
-        <v>4.022078841585339</v>
+        <v>4.017674725761164</v>
       </c>
       <c r="N10" t="n">
-        <v>24.34764623906005</v>
+        <v>24.2802469277409</v>
       </c>
       <c r="O10" t="n">
-        <v>4.934333413852376</v>
+        <v>4.92749905405784</v>
       </c>
       <c r="P10" t="n">
-        <v>263.4348994596086</v>
+        <v>263.4011754140142</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32791,28 +32943,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001460409521546004</v>
+        <v>0.007305568398677728</v>
       </c>
       <c r="J11" t="n">
+        <v>415</v>
+      </c>
+      <c r="K11" t="n">
         <v>413</v>
       </c>
-      <c r="K11" t="n">
-        <v>411</v>
-      </c>
       <c r="L11" t="n">
-        <v>5.039864815814532e-06</v>
+        <v>0.0001268526491787769</v>
       </c>
       <c r="M11" t="n">
-        <v>3.650539337304915</v>
+        <v>3.654854025201572</v>
       </c>
       <c r="N11" t="n">
-        <v>23.28161379159813</v>
+        <v>23.32019547028031</v>
       </c>
       <c r="O11" t="n">
-        <v>4.82510246436261</v>
+        <v>4.829098825897055</v>
       </c>
       <c r="P11" t="n">
-        <v>282.5124483863473</v>
+        <v>282.4538226300828</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32869,28 +33021,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.005993407381409852</v>
+        <v>-0.001488524419670635</v>
       </c>
       <c r="J12" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K12" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L12" t="n">
-        <v>7.515276745229116e-05</v>
+        <v>4.677961106813733e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>3.912274077361457</v>
+        <v>3.911641875697007</v>
       </c>
       <c r="N12" t="n">
-        <v>26.17355376698224</v>
+        <v>26.13704189250671</v>
       </c>
       <c r="O12" t="n">
-        <v>5.116009555012797</v>
+        <v>5.112439915784508</v>
       </c>
       <c r="P12" t="n">
-        <v>311.9695105833831</v>
+        <v>311.924257535553</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32947,28 +33099,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09212505353369889</v>
+        <v>-0.08486555998284831</v>
       </c>
       <c r="J13" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K13" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01837278599437486</v>
+        <v>0.01568253448199752</v>
       </c>
       <c r="M13" t="n">
-        <v>3.835528890826677</v>
+        <v>3.846402823724909</v>
       </c>
       <c r="N13" t="n">
-        <v>24.83246286062823</v>
+        <v>24.94508839852231</v>
       </c>
       <c r="O13" t="n">
-        <v>4.983218122923001</v>
+        <v>4.99450582125222</v>
       </c>
       <c r="P13" t="n">
-        <v>301.8254827283156</v>
+        <v>301.7525573197576</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33025,28 +33177,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1813550545882852</v>
+        <v>-0.1741605294654849</v>
       </c>
       <c r="J14" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K14" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08416103316605095</v>
+        <v>0.0781863309568559</v>
       </c>
       <c r="M14" t="n">
-        <v>3.596122869452754</v>
+        <v>3.608299355362496</v>
       </c>
       <c r="N14" t="n">
-        <v>19.60018194843302</v>
+        <v>19.73399108261199</v>
       </c>
       <c r="O14" t="n">
-        <v>4.427209273168936</v>
+        <v>4.442295699591821</v>
       </c>
       <c r="P14" t="n">
-        <v>298.1551435962246</v>
+        <v>298.0828712411776</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33103,28 +33255,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3173229363611771</v>
+        <v>-0.3077407401153334</v>
       </c>
       <c r="J15" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K15" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2482820875684012</v>
+        <v>0.2349207222878377</v>
       </c>
       <c r="M15" t="n">
-        <v>3.196328067570966</v>
+        <v>3.217236803311385</v>
       </c>
       <c r="N15" t="n">
-        <v>16.73395599077902</v>
+        <v>17.05860311158843</v>
       </c>
       <c r="O15" t="n">
-        <v>4.090715828651389</v>
+        <v>4.130206182696988</v>
       </c>
       <c r="P15" t="n">
-        <v>309.1580482626777</v>
+        <v>309.0618632290339</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33181,28 +33333,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4091324598256253</v>
+        <v>-0.4012363197251363</v>
       </c>
       <c r="J16" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K16" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3541054424602873</v>
+        <v>0.3443548748838839</v>
       </c>
       <c r="M16" t="n">
-        <v>3.252753746097333</v>
+        <v>3.271637110219073</v>
       </c>
       <c r="N16" t="n">
-        <v>16.75880625923479</v>
+        <v>16.95319052851456</v>
       </c>
       <c r="O16" t="n">
-        <v>4.093752100364015</v>
+        <v>4.11742523047044</v>
       </c>
       <c r="P16" t="n">
-        <v>315.8661703377825</v>
+        <v>315.7869097217471</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33259,28 +33411,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3935486537364791</v>
+        <v>-0.3904717835243803</v>
       </c>
       <c r="J17" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K17" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3206140009962857</v>
+        <v>0.319391432360159</v>
       </c>
       <c r="M17" t="n">
-        <v>3.426238814172058</v>
+        <v>3.422059913704188</v>
       </c>
       <c r="N17" t="n">
-        <v>17.97312875589529</v>
+        <v>17.92902227181613</v>
       </c>
       <c r="O17" t="n">
-        <v>4.239472697859404</v>
+        <v>4.234267619295706</v>
       </c>
       <c r="P17" t="n">
-        <v>310.9929990590462</v>
+        <v>310.9620857947101</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33337,28 +33489,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3139794124057295</v>
+        <v>-0.3087009491867742</v>
       </c>
       <c r="J18" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K18" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2668310992784523</v>
+        <v>0.2610478260662425</v>
       </c>
       <c r="M18" t="n">
-        <v>2.938651970592546</v>
+        <v>2.94943667494655</v>
       </c>
       <c r="N18" t="n">
-        <v>14.83414940741191</v>
+        <v>14.88590779716171</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85151261291092</v>
+        <v>3.858225990939581</v>
       </c>
       <c r="P18" t="n">
-        <v>318.181511873073</v>
+        <v>318.1284885531561</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33415,28 +33567,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2613093301788146</v>
+        <v>-0.2598930262145036</v>
       </c>
       <c r="J19" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K19" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2513512031279963</v>
+        <v>0.2514931696078552</v>
       </c>
       <c r="M19" t="n">
-        <v>2.606763594274438</v>
+        <v>2.600519619707384</v>
       </c>
       <c r="N19" t="n">
-        <v>11.13780757898775</v>
+        <v>11.09333096876839</v>
       </c>
       <c r="O19" t="n">
-        <v>3.337335401032949</v>
+        <v>3.330665244176963</v>
       </c>
       <c r="P19" t="n">
-        <v>320.1249104082472</v>
+        <v>320.1106800644456</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33474,7 +33626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T414"/>
+  <dimension ref="A1:T416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75637,6 +75789,210 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-38.528394290091,178.28917247804586</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-38.52867332834122,178.28831174851223</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-38.5290488507053,178.28754750065252</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-38.529453846994336,178.28681272733255</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-38.52989588118857,178.28611499158217</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-38.530363067532605,178.28535875333006</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-38.53088902150055,178.28454760056724</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-38.53147324631236,178.2838845578176</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-38.53210594029274,178.2834775595676</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-38.53276855536625,178.28312685722176</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-38.533545918279366,178.28280866020174</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-38.53430201475864,178.2825001225485</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-38.53499158418823,178.28228038460972</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-38.53568937487463,178.28223881625138</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-38.53637213338661,178.2820955006997</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-38.537039184185986,178.28179592597374</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>-38.53774485098712,178.28173959423444</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>-38.53842942932701,178.28153495221423</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-38.528378385676525,178.2891565744573</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-38.52866074610845,178.28829916704956</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-38.52903768215247,178.2875363328451</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-38.52944875750429,178.28680763820404</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-38.529892417493535,178.28611152814335</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-38.53035885783983,178.28535393149738</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-38.530887207986,178.2845447582969</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-38.531472944041276,178.2838839891993</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-38.5321035221167,178.2834730105849</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-38.53276815233612,178.2831260990513</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-38.533544450185865,178.28280386175803</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-38.53430149361815,178.2824953622102</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-38.53499099041463,178.28227459743226</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-38.53568937487463,178.28223881625138</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-38.53637213338661,178.2820955006997</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-38.537040496808224,178.28180516015973</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-38.537743762475486,178.2817319365402</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>-38.538430293737,178.28154103338272</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T416"/>
+  <dimension ref="A1:T418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27869,10 +27869,10 @@
         <v>300.02</v>
       </c>
       <c r="O416" t="n">
-        <v>309.97</v>
+        <v>309.28</v>
       </c>
       <c r="P416" t="n">
-        <v>312.61</v>
+        <v>311.62</v>
       </c>
       <c r="Q416" t="n">
         <v>303.91</v>
@@ -27884,6 +27884,138 @@
         <v>314.82</v>
       </c>
       <c r="T416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>290.02</v>
+      </c>
+      <c r="C417" t="n">
+        <v>269.76</v>
+      </c>
+      <c r="D417" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="E417" t="n">
+        <v>263.06</v>
+      </c>
+      <c r="F417" t="n">
+        <v>269.52</v>
+      </c>
+      <c r="G417" t="n">
+        <v>273.51</v>
+      </c>
+      <c r="H417" t="n">
+        <v>266.66</v>
+      </c>
+      <c r="I417" t="n">
+        <v>259.11</v>
+      </c>
+      <c r="J417" t="n">
+        <v>270.08</v>
+      </c>
+      <c r="K417" t="n">
+        <v>292.86</v>
+      </c>
+      <c r="L417" t="n">
+        <v>319.95</v>
+      </c>
+      <c r="M417" t="n">
+        <v>310.06</v>
+      </c>
+      <c r="N417" t="n">
+        <v>302.79</v>
+      </c>
+      <c r="O417" t="n">
+        <v>311.89</v>
+      </c>
+      <c r="P417" t="n">
+        <v>313.82</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>307.02</v>
+      </c>
+      <c r="R417" t="n">
+        <v>315.27</v>
+      </c>
+      <c r="S417" t="n">
+        <v>315.27</v>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>290.46</v>
+      </c>
+      <c r="C418" t="n">
+        <v>268.49</v>
+      </c>
+      <c r="D418" t="n">
+        <v>262.89</v>
+      </c>
+      <c r="E418" t="n">
+        <v>261.91</v>
+      </c>
+      <c r="F418" t="n">
+        <v>267.89</v>
+      </c>
+      <c r="G418" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="H418" t="n">
+        <v>265.44</v>
+      </c>
+      <c r="I418" t="n">
+        <v>258.01</v>
+      </c>
+      <c r="J418" t="n">
+        <v>270.48</v>
+      </c>
+      <c r="K418" t="n">
+        <v>292.28</v>
+      </c>
+      <c r="L418" t="n">
+        <v>319.51</v>
+      </c>
+      <c r="M418" t="n">
+        <v>309.54</v>
+      </c>
+      <c r="N418" t="n">
+        <v>301.94</v>
+      </c>
+      <c r="O418" t="n">
+        <v>311.17</v>
+      </c>
+      <c r="P418" t="n">
+        <v>313.56</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>306.98</v>
+      </c>
+      <c r="R418" t="n">
+        <v>314.58</v>
+      </c>
+      <c r="S418" t="n">
+        <v>315.72</v>
+      </c>
+      <c r="T418" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27900,7 +28032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B417"/>
+  <dimension ref="A1:B419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32073,6 +32205,26 @@
       </c>
       <c r="B417" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -32241,28 +32393,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3140306415661454</v>
+        <v>-0.305034593332736</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0453100530821996</v>
+        <v>0.04323710600848374</v>
       </c>
       <c r="M2" t="n">
-        <v>8.394507329582645</v>
+        <v>8.39439256405819</v>
       </c>
       <c r="N2" t="n">
-        <v>114.4907791464184</v>
+        <v>114.2992311663916</v>
       </c>
       <c r="O2" t="n">
-        <v>10.7000364086492</v>
+        <v>10.69108185201065</v>
       </c>
       <c r="P2" t="n">
-        <v>289.8702863838548</v>
+        <v>289.779341044643</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32319,28 +32471,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3969389020491227</v>
+        <v>-0.3883751686113525</v>
       </c>
       <c r="J3" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K3" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09728543770419551</v>
+        <v>0.09421846695428115</v>
       </c>
       <c r="M3" t="n">
-        <v>7.078505278875324</v>
+        <v>7.084371433868192</v>
       </c>
       <c r="N3" t="n">
-        <v>80.55798950261389</v>
+        <v>80.49849336449115</v>
       </c>
       <c r="O3" t="n">
-        <v>8.975410269319942</v>
+        <v>8.972095260555983</v>
       </c>
       <c r="P3" t="n">
-        <v>271.3812064100805</v>
+        <v>271.2946353327009</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32397,28 +32549,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2367050350475273</v>
+        <v>-0.2263756252991441</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04496537392486233</v>
+        <v>0.04148295731581952</v>
       </c>
       <c r="M4" t="n">
-        <v>6.649791530892129</v>
+        <v>6.66393024054618</v>
       </c>
       <c r="N4" t="n">
-        <v>65.20540812393442</v>
+        <v>65.37060849133528</v>
       </c>
       <c r="O4" t="n">
-        <v>8.074986571130284</v>
+        <v>8.08520924227291</v>
       </c>
       <c r="P4" t="n">
-        <v>260.1017943665768</v>
+        <v>259.9972490860713</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32475,28 +32627,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.268858372084804</v>
+        <v>-0.2615733157863609</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05672756479735519</v>
+        <v>0.05430154309223989</v>
       </c>
       <c r="M5" t="n">
-        <v>6.639653359512329</v>
+        <v>6.641745644767937</v>
       </c>
       <c r="N5" t="n">
-        <v>66.32744634739625</v>
+        <v>66.24943531979807</v>
       </c>
       <c r="O5" t="n">
-        <v>8.14416639978557</v>
+        <v>8.139375609946875</v>
       </c>
       <c r="P5" t="n">
-        <v>262.5301001665248</v>
+        <v>262.4567632771971</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32553,28 +32705,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1407418296428923</v>
+        <v>-0.1313091891058163</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K6" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01835404616118452</v>
+        <v>0.01609899525224978</v>
       </c>
       <c r="M6" t="n">
-        <v>6.10672497537668</v>
+        <v>6.117799051210722</v>
       </c>
       <c r="N6" t="n">
-        <v>58.86432906455335</v>
+        <v>58.9865282166452</v>
       </c>
       <c r="O6" t="n">
-        <v>7.672309239372026</v>
+        <v>7.680268759401926</v>
       </c>
       <c r="P6" t="n">
-        <v>263.2362762463209</v>
+        <v>263.1415486572159</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32631,28 +32783,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.001407328818127536</v>
+        <v>0.009624540481206943</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L7" t="n">
-        <v>1.753801713633152e-06</v>
+        <v>8.230322608748786e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>6.440208078853118</v>
+        <v>6.460528341608268</v>
       </c>
       <c r="N7" t="n">
-        <v>62.45946722708535</v>
+        <v>62.71034558193154</v>
       </c>
       <c r="O7" t="n">
-        <v>7.903130217014354</v>
+        <v>7.918986398645444</v>
       </c>
       <c r="P7" t="n">
-        <v>262.0463920602051</v>
+        <v>261.9354226974489</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32709,28 +32861,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03363978061357423</v>
+        <v>0.04331964106372881</v>
       </c>
       <c r="J8" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K8" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001464283687964585</v>
+        <v>0.002431614026622064</v>
       </c>
       <c r="M8" t="n">
-        <v>5.326998588881999</v>
+        <v>5.346898852754835</v>
       </c>
       <c r="N8" t="n">
-        <v>42.58413535730306</v>
+        <v>42.80283478538195</v>
       </c>
       <c r="O8" t="n">
-        <v>6.525652102074019</v>
+        <v>6.542387544725698</v>
       </c>
       <c r="P8" t="n">
-        <v>255.7061133305474</v>
+        <v>255.6086678816816</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32787,28 +32939,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07324300453587379</v>
+        <v>0.07950368967353531</v>
       </c>
       <c r="J9" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K9" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01045797327196074</v>
+        <v>0.01237171055929398</v>
       </c>
       <c r="M9" t="n">
-        <v>4.399103382469713</v>
+        <v>4.411915565139856</v>
       </c>
       <c r="N9" t="n">
-        <v>28.0105840085846</v>
+        <v>28.05389292561806</v>
       </c>
       <c r="O9" t="n">
-        <v>5.292502622444754</v>
+        <v>5.29659257689489</v>
       </c>
       <c r="P9" t="n">
-        <v>250.4951978752711</v>
+        <v>250.4321733638704</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32865,28 +33017,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08686577007052289</v>
+        <v>0.09154434375154788</v>
       </c>
       <c r="J10" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K10" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0168601980703208</v>
+        <v>0.01884186926983378</v>
       </c>
       <c r="M10" t="n">
-        <v>4.017674725761164</v>
+        <v>4.019177820937409</v>
       </c>
       <c r="N10" t="n">
-        <v>24.2802469277409</v>
+        <v>24.26234917683662</v>
       </c>
       <c r="O10" t="n">
-        <v>4.92749905405784</v>
+        <v>4.925682610241611</v>
       </c>
       <c r="P10" t="n">
-        <v>263.4011754140142</v>
+        <v>263.354074860957</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32943,28 +33095,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007305568398677728</v>
+        <v>0.01746121834071271</v>
       </c>
       <c r="J11" t="n">
+        <v>417</v>
+      </c>
+      <c r="K11" t="n">
         <v>415</v>
       </c>
-      <c r="K11" t="n">
-        <v>413</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0001268526491787769</v>
+        <v>0.0007187393947286624</v>
       </c>
       <c r="M11" t="n">
-        <v>3.654854025201572</v>
+        <v>3.676313675582569</v>
       </c>
       <c r="N11" t="n">
-        <v>23.32019547028031</v>
+        <v>23.67442275300473</v>
       </c>
       <c r="O11" t="n">
-        <v>4.829098825897055</v>
+        <v>4.86563693189337</v>
       </c>
       <c r="P11" t="n">
-        <v>282.4538226300828</v>
+        <v>282.3517463661724</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33021,28 +33173,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.001488524419670635</v>
+        <v>0.006544942966409509</v>
       </c>
       <c r="J12" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K12" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L12" t="n">
-        <v>4.677961106813733e-06</v>
+        <v>9.053966981542594e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.911641875697007</v>
+        <v>3.925126936473224</v>
       </c>
       <c r="N12" t="n">
-        <v>26.13704189250671</v>
+        <v>26.30197133267529</v>
       </c>
       <c r="O12" t="n">
-        <v>5.112439915784508</v>
+        <v>5.12854475779195</v>
       </c>
       <c r="P12" t="n">
-        <v>311.924257535553</v>
+        <v>311.8433847642244</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33099,28 +33251,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08486555998284831</v>
+        <v>-0.07430745559243745</v>
       </c>
       <c r="J13" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K13" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01568253448199752</v>
+        <v>0.0119758739370317</v>
       </c>
       <c r="M13" t="n">
-        <v>3.846402823724909</v>
+        <v>3.870348668256015</v>
       </c>
       <c r="N13" t="n">
-        <v>24.94508839852231</v>
+        <v>25.32677611408109</v>
       </c>
       <c r="O13" t="n">
-        <v>4.99450582125222</v>
+        <v>5.032571521010018</v>
       </c>
       <c r="P13" t="n">
-        <v>301.7525573197576</v>
+        <v>301.646268938613</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33177,28 +33329,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1741605294654849</v>
+        <v>-0.1650278884882142</v>
       </c>
       <c r="J14" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K14" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0781863309568559</v>
+        <v>0.07033009701706761</v>
       </c>
       <c r="M14" t="n">
-        <v>3.608299355362496</v>
+        <v>3.628809575347527</v>
       </c>
       <c r="N14" t="n">
-        <v>19.73399108261199</v>
+        <v>20.01506648730804</v>
       </c>
       <c r="O14" t="n">
-        <v>4.442295699591821</v>
+        <v>4.473820122368359</v>
       </c>
       <c r="P14" t="n">
-        <v>298.0828712411776</v>
+        <v>297.9909338704036</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33255,28 +33407,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3077407401153334</v>
+        <v>-0.2971764136995517</v>
       </c>
       <c r="J15" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K15" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2349207222878377</v>
+        <v>0.21962195268582</v>
       </c>
       <c r="M15" t="n">
-        <v>3.217236803311385</v>
+        <v>3.243238990478744</v>
       </c>
       <c r="N15" t="n">
-        <v>17.05860311158843</v>
+        <v>17.48597129782916</v>
       </c>
       <c r="O15" t="n">
-        <v>4.130206182696988</v>
+        <v>4.181623045879333</v>
       </c>
       <c r="P15" t="n">
-        <v>309.0618632290339</v>
+        <v>308.9555907231932</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33333,28 +33485,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4012363197251363</v>
+        <v>-0.3929531864367205</v>
       </c>
       <c r="J16" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K16" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3443548748838839</v>
+        <v>0.333607212706162</v>
       </c>
       <c r="M16" t="n">
-        <v>3.271637110219073</v>
+        <v>3.292617879929516</v>
       </c>
       <c r="N16" t="n">
-        <v>16.95319052851456</v>
+        <v>17.18732451422296</v>
       </c>
       <c r="O16" t="n">
-        <v>4.11742523047044</v>
+        <v>4.145759823509191</v>
       </c>
       <c r="P16" t="n">
-        <v>315.7869097217471</v>
+        <v>315.7035813403311</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33411,28 +33563,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3904717835243803</v>
+        <v>-0.3838833323497223</v>
       </c>
       <c r="J17" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K17" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L17" t="n">
-        <v>0.319391432360159</v>
+        <v>0.3123440727998801</v>
       </c>
       <c r="M17" t="n">
-        <v>3.422059913704188</v>
+        <v>3.432213769578002</v>
       </c>
       <c r="N17" t="n">
-        <v>17.92902227181613</v>
+        <v>18.03811827494478</v>
       </c>
       <c r="O17" t="n">
-        <v>4.234267619295706</v>
+        <v>4.247130593111634</v>
       </c>
       <c r="P17" t="n">
-        <v>310.9620857947101</v>
+        <v>310.8957592387583</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33489,28 +33641,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3087009491867742</v>
+        <v>-0.3035674950861683</v>
       </c>
       <c r="J18" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K18" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2610478260662425</v>
+        <v>0.2554461491955908</v>
       </c>
       <c r="M18" t="n">
-        <v>2.94943667494655</v>
+        <v>2.95982057819682</v>
       </c>
       <c r="N18" t="n">
-        <v>14.88590779716171</v>
+        <v>14.93351643739881</v>
       </c>
       <c r="O18" t="n">
-        <v>3.858225990939581</v>
+        <v>3.864390823583817</v>
       </c>
       <c r="P18" t="n">
-        <v>318.1284885531561</v>
+        <v>318.0768110512708</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33567,28 +33719,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2598930262145036</v>
+        <v>-0.2575338159221169</v>
       </c>
       <c r="J19" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K19" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2514931696078552</v>
+        <v>0.2499472150563113</v>
       </c>
       <c r="M19" t="n">
-        <v>2.600519619707384</v>
+        <v>2.598476098271001</v>
       </c>
       <c r="N19" t="n">
-        <v>11.09333096876839</v>
+        <v>11.06539312476336</v>
       </c>
       <c r="O19" t="n">
-        <v>3.330665244176963</v>
+        <v>3.326468566627882</v>
       </c>
       <c r="P19" t="n">
-        <v>320.1106800644456</v>
+        <v>320.0869286278851</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33626,7 +33778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T416"/>
+  <dimension ref="A1:T418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75964,12 +76116,12 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>-38.53568937487463,178.28223881625138</t>
+          <t>-38.535688482303925,178.28223100214396</t>
         </is>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>-38.53637213338661,178.2820955006997</t>
+          <t>-38.536370636706565,178.28208433250416</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
@@ -75988,6 +76140,210 @@
         </is>
       </c>
       <c r="T416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-38.52840630675792,178.28918449409528</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-38.528675590315466,178.28831401034873</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-38.52905266780534,178.28755131749892</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-38.52945321080809,178.28681209119145</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-38.52991136178319,178.2861304710374</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-38.53038298004432,178.2853815613716</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-38.53090528645567,178.2845730921853</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-38.53148906516144,178.28391431551583</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-38.532110726265586,178.2834865627634</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-38.5327918807255,178.28317073635137</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-38.533557565147056,178.28284672786143</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-38.53430632036405,178.28253945201186</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-38.53499421541673,178.28230602974995</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-38.53569185854682,178.2822605598553</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-38.53637396266072,178.2821091507169</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-38.53704547516127,178.2818401825017</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-38.53774485098712,178.28173959423444</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>-38.53843101407839,178.28154610102325</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-38.52840941695382,178.28918760413228</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-38.52866661310484,178.2883050336861</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-38.52903952001569,178.28753817058532</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-38.52944508176132,178.28680396272281</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-38.52989983969703,178.28611894979838</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-38.53037322425067,178.28537038696038</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-38.530898372433725,178.28456225602574</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-38.53148352352737,178.28390389084305</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-38.532112741411815,178.28349035358303</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-38.53278895875927,178.28316523961223</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-38.53355612967949,178.28284203604844</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-38.5343056751445,178.28253355825922</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-38.534993225796065,178.2822963844537</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-38.53569092717023,178.28225240600372</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-38.53637356959369,178.28210621765533</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-38.53704541113108,178.28183973205356</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-38.53774374646796,178.28173182392703</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>-38.538431734419575,178.28155116866384</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T418"/>
+  <dimension ref="A1:T420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28016,6 +28016,138 @@
         <v>315.72</v>
       </c>
       <c r="T418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>290.46</v>
+      </c>
+      <c r="C419" t="n">
+        <v>268.49</v>
+      </c>
+      <c r="D419" t="n">
+        <v>262.89</v>
+      </c>
+      <c r="E419" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="F419" t="n">
+        <v>266.11</v>
+      </c>
+      <c r="G419" t="n">
+        <v>270.06</v>
+      </c>
+      <c r="H419" t="n">
+        <v>263.8</v>
+      </c>
+      <c r="I419" t="n">
+        <v>257.35</v>
+      </c>
+      <c r="J419" t="n">
+        <v>269.06</v>
+      </c>
+      <c r="K419" t="n">
+        <v>291.27</v>
+      </c>
+      <c r="L419" t="n">
+        <v>318.81</v>
+      </c>
+      <c r="M419" t="n">
+        <v>308.66</v>
+      </c>
+      <c r="N419" t="n">
+        <v>301.17</v>
+      </c>
+      <c r="O419" t="n">
+        <v>309.87</v>
+      </c>
+      <c r="P419" t="n">
+        <v>312.71</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>306.31</v>
+      </c>
+      <c r="R419" t="n">
+        <v>313.66</v>
+      </c>
+      <c r="S419" t="n">
+        <v>314.56</v>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>285.82</v>
+      </c>
+      <c r="C420" t="n">
+        <v>263.71</v>
+      </c>
+      <c r="D420" t="n">
+        <v>257.16</v>
+      </c>
+      <c r="E420" t="n">
+        <v>256.94</v>
+      </c>
+      <c r="F420" t="n">
+        <v>263.58</v>
+      </c>
+      <c r="G420" t="n">
+        <v>268.97</v>
+      </c>
+      <c r="H420" t="n">
+        <v>262.11</v>
+      </c>
+      <c r="I420" t="n">
+        <v>256.32</v>
+      </c>
+      <c r="J420" t="n">
+        <v>266.64</v>
+      </c>
+      <c r="K420" t="n">
+        <v>290.27</v>
+      </c>
+      <c r="L420" t="n">
+        <v>316.91</v>
+      </c>
+      <c r="M420" t="n">
+        <v>307.84</v>
+      </c>
+      <c r="N420" t="n">
+        <v>300.86</v>
+      </c>
+      <c r="O420" t="n">
+        <v>308.89</v>
+      </c>
+      <c r="P420" t="n">
+        <v>313.26</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>305.44</v>
+      </c>
+      <c r="R420" t="n">
+        <v>313.97</v>
+      </c>
+      <c r="S420" t="n">
+        <v>315.17</v>
+      </c>
+      <c r="T420" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28032,7 +28164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B419"/>
+  <dimension ref="A1:B421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32225,6 +32357,26 @@
       </c>
       <c r="B419" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>
@@ -32393,28 +32545,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.305034593332736</v>
+        <v>-0.2984039102955873</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K2" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04323710600848374</v>
+        <v>0.04186361113879566</v>
       </c>
       <c r="M2" t="n">
-        <v>8.39439256405819</v>
+        <v>8.383625181714024</v>
       </c>
       <c r="N2" t="n">
-        <v>114.2992311663916</v>
+        <v>113.9745453513506</v>
       </c>
       <c r="O2" t="n">
-        <v>10.69108185201065</v>
+        <v>10.67588616234505</v>
       </c>
       <c r="P2" t="n">
-        <v>289.779341044643</v>
+        <v>289.7121310487715</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32471,28 +32623,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3883751686113525</v>
+        <v>-0.3830981712686963</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09421846695428115</v>
+        <v>0.09277265924037614</v>
       </c>
       <c r="M3" t="n">
-        <v>7.084371433868192</v>
+        <v>7.074892903844463</v>
       </c>
       <c r="N3" t="n">
-        <v>80.49849336449115</v>
+        <v>80.26468104371578</v>
       </c>
       <c r="O3" t="n">
-        <v>8.972095260555983</v>
+        <v>8.959055812066124</v>
       </c>
       <c r="P3" t="n">
-        <v>271.2946353327009</v>
+        <v>271.241158438757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32549,28 +32701,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2263756252991441</v>
+        <v>-0.2201865379541791</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K4" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04148295731581952</v>
+        <v>0.03967472385715998</v>
       </c>
       <c r="M4" t="n">
-        <v>6.66393024054618</v>
+        <v>6.659772991586946</v>
       </c>
       <c r="N4" t="n">
-        <v>65.37060849133528</v>
+        <v>65.27040509840161</v>
       </c>
       <c r="O4" t="n">
-        <v>8.08520924227291</v>
+        <v>8.07901015585459</v>
       </c>
       <c r="P4" t="n">
-        <v>259.9972490860713</v>
+        <v>259.9344570154831</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32627,28 +32779,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2615733157863609</v>
+        <v>-0.2583828576076585</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K5" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05430154309223989</v>
+        <v>0.05362541366310702</v>
       </c>
       <c r="M5" t="n">
-        <v>6.641745644767937</v>
+        <v>6.624758192191771</v>
       </c>
       <c r="N5" t="n">
-        <v>66.24943531979807</v>
+        <v>65.9930749758165</v>
       </c>
       <c r="O5" t="n">
-        <v>8.139375609946875</v>
+        <v>8.123612187679598</v>
       </c>
       <c r="P5" t="n">
-        <v>262.4567632771971</v>
+        <v>262.4245717178322</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32705,28 +32857,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1313091891058163</v>
+        <v>-0.1260327307254078</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01609899525224978</v>
+        <v>0.01499511681204901</v>
       </c>
       <c r="M6" t="n">
-        <v>6.117799051210722</v>
+        <v>6.110971315508977</v>
       </c>
       <c r="N6" t="n">
-        <v>58.9865282166452</v>
+        <v>58.83890083768753</v>
       </c>
       <c r="O6" t="n">
-        <v>7.680268759401926</v>
+        <v>7.670651917385348</v>
       </c>
       <c r="P6" t="n">
-        <v>263.1415486572159</v>
+        <v>263.0884028961968</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32783,28 +32935,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009624540481206943</v>
+        <v>0.01704724207592976</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K7" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>8.230322608748786e-05</v>
+        <v>0.0002602706523970877</v>
       </c>
       <c r="M7" t="n">
-        <v>6.460528341608268</v>
+        <v>6.463866436780719</v>
       </c>
       <c r="N7" t="n">
-        <v>62.71034558193154</v>
+        <v>62.66388988512453</v>
       </c>
       <c r="O7" t="n">
-        <v>7.918986398645444</v>
+        <v>7.916052670689131</v>
       </c>
       <c r="P7" t="n">
-        <v>261.9354226974489</v>
+        <v>261.860512431276</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32861,28 +33013,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04331964106372881</v>
+        <v>0.04959545743129815</v>
       </c>
       <c r="J8" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K8" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002431614026622064</v>
+        <v>0.003210016150240413</v>
       </c>
       <c r="M8" t="n">
-        <v>5.346898852754835</v>
+        <v>5.351120544196577</v>
       </c>
       <c r="N8" t="n">
-        <v>42.80283478538195</v>
+        <v>42.78177558203086</v>
       </c>
       <c r="O8" t="n">
-        <v>6.542387544725698</v>
+        <v>6.540777903432501</v>
       </c>
       <c r="P8" t="n">
-        <v>255.6086678816816</v>
+        <v>255.5452918972459</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32939,28 +33091,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07950368967353531</v>
+        <v>0.0838447646860077</v>
       </c>
       <c r="J9" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K9" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01237171055929398</v>
+        <v>0.01386423735446418</v>
       </c>
       <c r="M9" t="n">
-        <v>4.411915565139856</v>
+        <v>4.414223800911013</v>
       </c>
       <c r="N9" t="n">
-        <v>28.05389292561806</v>
+        <v>28.00729600200707</v>
       </c>
       <c r="O9" t="n">
-        <v>5.29659257689489</v>
+        <v>5.292191984613472</v>
       </c>
       <c r="P9" t="n">
-        <v>250.4321733638704</v>
+        <v>250.3883337746272</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33017,28 +33169,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09154434375154788</v>
+        <v>0.09361882550718809</v>
       </c>
       <c r="J10" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K10" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01884186926983378</v>
+        <v>0.01990383846172694</v>
       </c>
       <c r="M10" t="n">
-        <v>4.019177820937409</v>
+        <v>4.009131576476165</v>
       </c>
       <c r="N10" t="n">
-        <v>24.26234917683662</v>
+        <v>24.17334685569911</v>
       </c>
       <c r="O10" t="n">
-        <v>4.925682610241611</v>
+        <v>4.916639793161495</v>
       </c>
       <c r="P10" t="n">
-        <v>263.354074860957</v>
+        <v>263.333146419678</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33095,28 +33247,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01746121834071271</v>
+        <v>0.02552001521579328</v>
       </c>
       <c r="J11" t="n">
+        <v>419</v>
+      </c>
+      <c r="K11" t="n">
         <v>417</v>
       </c>
-      <c r="K11" t="n">
-        <v>415</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0007187393947286624</v>
+        <v>0.001533359890056984</v>
       </c>
       <c r="M11" t="n">
-        <v>3.676313675582569</v>
+        <v>3.690621734219656</v>
       </c>
       <c r="N11" t="n">
-        <v>23.67442275300473</v>
+        <v>23.86012409656509</v>
       </c>
       <c r="O11" t="n">
-        <v>4.86563693189337</v>
+        <v>4.884682599367649</v>
       </c>
       <c r="P11" t="n">
-        <v>282.3517463661724</v>
+        <v>282.2704779467465</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33173,28 +33325,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>0.006544942966409509</v>
+        <v>0.01247082581654893</v>
       </c>
       <c r="J12" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K12" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L12" t="n">
-        <v>9.053966981542594e-05</v>
+        <v>0.0003305911007637219</v>
       </c>
       <c r="M12" t="n">
-        <v>3.925126936473224</v>
+        <v>3.930394974798144</v>
       </c>
       <c r="N12" t="n">
-        <v>26.30197133267529</v>
+        <v>26.34111942836019</v>
       </c>
       <c r="O12" t="n">
-        <v>5.12854475779195</v>
+        <v>5.132360025208694</v>
       </c>
       <c r="P12" t="n">
-        <v>311.8433847642244</v>
+        <v>311.7835459097388</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33251,28 +33403,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07430745559243745</v>
+        <v>-0.06559674291458779</v>
       </c>
       <c r="J13" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K13" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0119758739370317</v>
+        <v>0.00934387474869447</v>
       </c>
       <c r="M13" t="n">
-        <v>3.870348668256015</v>
+        <v>3.887172632530468</v>
       </c>
       <c r="N13" t="n">
-        <v>25.32677611408109</v>
+        <v>25.5528313957924</v>
       </c>
       <c r="O13" t="n">
-        <v>5.032571521010018</v>
+        <v>5.054980850190473</v>
       </c>
       <c r="P13" t="n">
-        <v>301.646268938613</v>
+        <v>301.5582873604699</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33329,28 +33481,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1650278884882142</v>
+        <v>-0.1574910003910416</v>
       </c>
       <c r="J14" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K14" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07033009701706761</v>
+        <v>0.06441395145802875</v>
       </c>
       <c r="M14" t="n">
-        <v>3.628809575347527</v>
+        <v>3.642695665749634</v>
       </c>
       <c r="N14" t="n">
-        <v>20.01506648730804</v>
+        <v>20.17873028744796</v>
       </c>
       <c r="O14" t="n">
-        <v>4.473820122368359</v>
+        <v>4.492074163173173</v>
       </c>
       <c r="P14" t="n">
-        <v>297.9909338704036</v>
+        <v>297.9148039626023</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33407,28 +33559,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2971764136995517</v>
+        <v>-0.2887021375176742</v>
       </c>
       <c r="J15" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K15" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L15" t="n">
-        <v>0.21962195268582</v>
+        <v>0.2087793878369502</v>
       </c>
       <c r="M15" t="n">
-        <v>3.243238990478744</v>
+        <v>3.262305806996274</v>
       </c>
       <c r="N15" t="n">
-        <v>17.48597129782916</v>
+        <v>17.73198334520122</v>
       </c>
       <c r="O15" t="n">
-        <v>4.181623045879333</v>
+        <v>4.210936160190656</v>
       </c>
       <c r="P15" t="n">
-        <v>308.9555907231932</v>
+        <v>308.8700645535818</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33485,28 +33637,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3929531864367205</v>
+        <v>-0.3850683594105731</v>
       </c>
       <c r="J16" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K16" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L16" t="n">
-        <v>0.333607212706162</v>
+        <v>0.3237134657777233</v>
       </c>
       <c r="M16" t="n">
-        <v>3.292617879929516</v>
+        <v>3.311527551211566</v>
       </c>
       <c r="N16" t="n">
-        <v>17.18732451422296</v>
+        <v>17.38973593335824</v>
       </c>
       <c r="O16" t="n">
-        <v>4.145759823509191</v>
+        <v>4.170100230612957</v>
       </c>
       <c r="P16" t="n">
-        <v>315.7035813403311</v>
+        <v>315.6239879206174</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33563,28 +33715,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3838833323497223</v>
+        <v>-0.3785794086956714</v>
       </c>
       <c r="J17" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K17" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3123440727998801</v>
+        <v>0.3074701826698543</v>
       </c>
       <c r="M17" t="n">
-        <v>3.432213769578002</v>
+        <v>3.437208783875583</v>
       </c>
       <c r="N17" t="n">
-        <v>18.03811827494478</v>
+        <v>18.08123143582584</v>
       </c>
       <c r="O17" t="n">
-        <v>4.247130593111634</v>
+        <v>4.252203127300699</v>
       </c>
       <c r="P17" t="n">
-        <v>310.8957592387583</v>
+        <v>310.8421913257245</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33641,28 +33793,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3035674950861683</v>
+        <v>-0.2996656531832488</v>
       </c>
       <c r="J18" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K18" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2554461491955908</v>
+        <v>0.2519748284210925</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95982057819682</v>
+        <v>2.964126079036582</v>
       </c>
       <c r="N18" t="n">
-        <v>14.93351643739881</v>
+        <v>14.9317787969914</v>
       </c>
       <c r="O18" t="n">
-        <v>3.864390823583817</v>
+        <v>3.86416598983421</v>
       </c>
       <c r="P18" t="n">
-        <v>318.0768110512708</v>
+        <v>318.0373931643669</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33719,28 +33871,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2575338159221169</v>
+        <v>-0.2558490416658883</v>
       </c>
       <c r="J19" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K19" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2499472150563113</v>
+        <v>0.2495469316777561</v>
       </c>
       <c r="M19" t="n">
-        <v>2.598476098271001</v>
+        <v>2.593425472601349</v>
       </c>
       <c r="N19" t="n">
-        <v>11.06539312476336</v>
+        <v>11.02598631907057</v>
       </c>
       <c r="O19" t="n">
-        <v>3.326468566627882</v>
+        <v>3.320540064367628</v>
       </c>
       <c r="P19" t="n">
-        <v>320.0869286278851</v>
+        <v>320.0699030126253</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33778,7 +33930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T418"/>
+  <dimension ref="A1:T420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76349,6 +76501,210 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-38.52840941695382,178.28918760413228</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-38.52866661310484,178.2883050336861</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-38.52903952001569,178.28753817058532</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-38.529433701094646,178.28679258286988</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-38.52988725729458,178.28610636832695</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-38.53035992696816,178.28535515608974</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-38.53088907817288,178.28454768938818</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-38.53148019854643,178.2838976360401</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-38.53210558764207,178.28347689617428</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-38.53278387050703,178.28315566770547</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-38.53355384598067,178.28283457180083</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-38.534304583233826,178.28252358421645</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-38.534992329315465,178.28228764695018</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-38.53568924551658,178.28223768377202</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-38.53637228456634,178.28209662880028</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-38.53704433862503,178.28183218704712</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-38.53774227377493,178.28172146351747</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-38.53842987753965,178.2815381054127</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-38.52837661851919,178.28915480739235</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-38.528632824855556,178.2882712475277</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-38.52899901632954,178.2874976696405</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-38.52940995013367,178.2867688336235</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-38.52986937331516,178.2860884856815</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-38.53035264353102,178.28534681355498</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-38.53087950054823,178.2845326786497</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-38.53147500956029,178.28388787475785</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-38.532093396002324,178.28345396172304</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-38.532778832632665,178.28314619057136</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-38.53354764736702,178.28281431170234</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-38.53430356577081,178.28251429022225</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-38.534991968394515,178.282284129254</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-38.53568797780719,178.28222658547463</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-38.536373116054726,178.28210283335352</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-38.53704294596719,178.2818223898002</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>-38.537742770008556,178.28172495452503</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>-38.538430854002556,178.28154497488092</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T420"/>
+  <dimension ref="A1:T423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28150,6 +28150,204 @@
       <c r="T420" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>285.59</v>
+      </c>
+      <c r="C421" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="D421" t="n">
+        <v>257.03</v>
+      </c>
+      <c r="E421" t="n">
+        <v>256.54</v>
+      </c>
+      <c r="F421" t="n">
+        <v>263.12</v>
+      </c>
+      <c r="G421" t="n">
+        <v>268.64</v>
+      </c>
+      <c r="H421" t="n">
+        <v>261.81</v>
+      </c>
+      <c r="I421" t="n">
+        <v>255.43</v>
+      </c>
+      <c r="J421" t="n">
+        <v>266.9</v>
+      </c>
+      <c r="K421" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="L421" t="n">
+        <v>316.72</v>
+      </c>
+      <c r="M421" t="n">
+        <v>307.34</v>
+      </c>
+      <c r="N421" t="n">
+        <v>300.3</v>
+      </c>
+      <c r="O421" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="P421" t="n">
+        <v>312.87</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>305.22</v>
+      </c>
+      <c r="R421" t="n">
+        <v>313.54</v>
+      </c>
+      <c r="S421" t="n">
+        <v>314.99</v>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:35+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>283.48</v>
+      </c>
+      <c r="C422" t="n">
+        <v>264.08</v>
+      </c>
+      <c r="D422" t="n">
+        <v>256.88</v>
+      </c>
+      <c r="E422" t="n">
+        <v>256</v>
+      </c>
+      <c r="F422" t="n">
+        <v>262.37</v>
+      </c>
+      <c r="G422" t="n">
+        <v>267.67</v>
+      </c>
+      <c r="H422" t="n">
+        <v>260.88</v>
+      </c>
+      <c r="I422" t="n">
+        <v>254.35</v>
+      </c>
+      <c r="J422" t="n">
+        <v>266.09</v>
+      </c>
+      <c r="K422" t="n">
+        <v>289.14</v>
+      </c>
+      <c r="L422" t="n">
+        <v>316.01</v>
+      </c>
+      <c r="M422" t="n">
+        <v>306.5</v>
+      </c>
+      <c r="N422" t="n">
+        <v>299.49</v>
+      </c>
+      <c r="O422" t="n">
+        <v>307.69</v>
+      </c>
+      <c r="P422" t="n">
+        <v>312.3</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>304.62</v>
+      </c>
+      <c r="R422" t="n">
+        <v>313.66</v>
+      </c>
+      <c r="S422" t="n">
+        <v>314.35</v>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:10+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>281.18</v>
+      </c>
+      <c r="C423" t="n">
+        <v>263.44</v>
+      </c>
+      <c r="D423" t="n">
+        <v>256.43</v>
+      </c>
+      <c r="E423" t="n">
+        <v>254.63</v>
+      </c>
+      <c r="F423" t="n">
+        <v>260.73</v>
+      </c>
+      <c r="G423" t="n">
+        <v>265.65</v>
+      </c>
+      <c r="H423" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="I423" t="n">
+        <v>254.3</v>
+      </c>
+      <c r="J423" t="n">
+        <v>266.19</v>
+      </c>
+      <c r="K423" t="n">
+        <v>287.01</v>
+      </c>
+      <c r="L423" t="n">
+        <v>315.54</v>
+      </c>
+      <c r="M423" t="n">
+        <v>306.12</v>
+      </c>
+      <c r="N423" t="n">
+        <v>299.13</v>
+      </c>
+      <c r="O423" t="n">
+        <v>308.42</v>
+      </c>
+      <c r="P423" t="n">
+        <v>312.05</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>305.33</v>
+      </c>
+      <c r="R423" t="n">
+        <v>313.04</v>
+      </c>
+      <c r="S423" t="n">
+        <v>313.92</v>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28164,7 +28362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B421"/>
+  <dimension ref="A1:B424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32377,6 +32575,36 @@
       </c>
       <c r="B421" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -32545,28 +32773,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2984039102955873</v>
+        <v>-0.2958425923004635</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K2" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04186361113879566</v>
+        <v>0.04188434402996755</v>
       </c>
       <c r="M2" t="n">
-        <v>8.383625181714024</v>
+        <v>8.337527008082668</v>
       </c>
       <c r="N2" t="n">
-        <v>113.9745453513506</v>
+        <v>113.1999844127553</v>
       </c>
       <c r="O2" t="n">
-        <v>10.67588616234505</v>
+        <v>10.63954813010192</v>
       </c>
       <c r="P2" t="n">
-        <v>289.7121310487715</v>
+        <v>289.6860687938174</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32623,28 +32851,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3830981712686963</v>
+        <v>-0.3786457727757333</v>
       </c>
       <c r="J3" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K3" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09277265924037614</v>
+        <v>0.09226740386922161</v>
       </c>
       <c r="M3" t="n">
-        <v>7.074892903844463</v>
+        <v>7.044702834800264</v>
       </c>
       <c r="N3" t="n">
-        <v>80.26468104371578</v>
+        <v>79.75071863319511</v>
       </c>
       <c r="O3" t="n">
-        <v>8.959055812066124</v>
+        <v>8.930325785389641</v>
       </c>
       <c r="P3" t="n">
-        <v>271.241158438757</v>
+        <v>271.1958236107764</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32701,28 +32929,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2201865379541791</v>
+        <v>-0.2160508685657465</v>
       </c>
       <c r="J4" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03967472385715998</v>
+        <v>0.0388988486675137</v>
       </c>
       <c r="M4" t="n">
-        <v>6.659772991586946</v>
+        <v>6.630518289198887</v>
       </c>
       <c r="N4" t="n">
-        <v>65.27040509840161</v>
+        <v>64.85817092680431</v>
       </c>
       <c r="O4" t="n">
-        <v>8.07901015585459</v>
+        <v>8.053457079217862</v>
       </c>
       <c r="P4" t="n">
-        <v>259.9344570154831</v>
+        <v>259.8922989462425</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32779,28 +33007,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2583828576076585</v>
+        <v>-0.258051630276898</v>
       </c>
       <c r="J5" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K5" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05362541366310702</v>
+        <v>0.05441637662721133</v>
       </c>
       <c r="M5" t="n">
-        <v>6.624758192191771</v>
+        <v>6.583295170534783</v>
       </c>
       <c r="N5" t="n">
-        <v>65.9930749758165</v>
+        <v>65.528809216358</v>
       </c>
       <c r="O5" t="n">
-        <v>8.123612187679598</v>
+        <v>8.09498667178384</v>
       </c>
       <c r="P5" t="n">
-        <v>262.4245717178322</v>
+        <v>262.4212213184962</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32857,28 +33085,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1260327307254078</v>
+        <v>-0.1225058306619242</v>
       </c>
       <c r="J6" t="n">
+        <v>422</v>
+      </c>
+      <c r="K6" t="n">
         <v>419</v>
       </c>
-      <c r="K6" t="n">
-        <v>416</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01499511681204901</v>
+        <v>0.01442318510644625</v>
       </c>
       <c r="M6" t="n">
-        <v>6.110971315508977</v>
+        <v>6.082064960705901</v>
       </c>
       <c r="N6" t="n">
-        <v>58.83890083768753</v>
+        <v>58.46363791698776</v>
       </c>
       <c r="O6" t="n">
-        <v>7.670651917385348</v>
+        <v>7.646151837165395</v>
       </c>
       <c r="P6" t="n">
-        <v>263.0884028961968</v>
+        <v>263.0527334504507</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32935,28 +33163,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01704724207592976</v>
+        <v>0.02452499650361923</v>
       </c>
       <c r="J7" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K7" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002602706523970877</v>
+        <v>0.0005467457489795047</v>
       </c>
       <c r="M7" t="n">
-        <v>6.463866436780719</v>
+        <v>6.452023069409544</v>
       </c>
       <c r="N7" t="n">
-        <v>62.66388988512453</v>
+        <v>62.40224766537934</v>
       </c>
       <c r="O7" t="n">
-        <v>7.916052670689131</v>
+        <v>7.899509330672339</v>
       </c>
       <c r="P7" t="n">
-        <v>261.860512431276</v>
+        <v>261.7847576530264</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33013,28 +33241,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04959545743129815</v>
+        <v>0.05591023981390594</v>
       </c>
       <c r="J8" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K8" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003210016150240413</v>
+        <v>0.004137987697133139</v>
       </c>
       <c r="M8" t="n">
-        <v>5.351120544196577</v>
+        <v>5.343529203025587</v>
       </c>
       <c r="N8" t="n">
-        <v>42.78177558203086</v>
+        <v>42.60312158101435</v>
       </c>
       <c r="O8" t="n">
-        <v>6.540777903432501</v>
+        <v>6.527106677618679</v>
       </c>
       <c r="P8" t="n">
-        <v>255.5452918972459</v>
+        <v>255.481265043639</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33091,28 +33319,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0838447646860077</v>
+        <v>0.0869185734164062</v>
       </c>
       <c r="J9" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K9" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01386423735446418</v>
+        <v>0.01513528308537915</v>
       </c>
       <c r="M9" t="n">
-        <v>4.414223800911013</v>
+        <v>4.399140837061529</v>
       </c>
       <c r="N9" t="n">
-        <v>28.00729600200707</v>
+        <v>27.83940508176076</v>
       </c>
       <c r="O9" t="n">
-        <v>5.292191984613472</v>
+        <v>5.276306007213831</v>
       </c>
       <c r="P9" t="n">
-        <v>250.3883337746272</v>
+        <v>250.3571701486619</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33169,28 +33397,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09361882550718809</v>
+        <v>0.09444373922536745</v>
       </c>
       <c r="J10" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K10" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01990383846172694</v>
+        <v>0.02060905217901177</v>
       </c>
       <c r="M10" t="n">
-        <v>4.009131576476165</v>
+        <v>3.984198502331735</v>
       </c>
       <c r="N10" t="n">
-        <v>24.17334685569911</v>
+        <v>24.00452705767179</v>
       </c>
       <c r="O10" t="n">
-        <v>4.916639793161495</v>
+        <v>4.899441504668852</v>
       </c>
       <c r="P10" t="n">
-        <v>263.333146419678</v>
+        <v>263.3247848489445</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33247,28 +33475,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02552001521579328</v>
+        <v>0.03408091030295499</v>
       </c>
       <c r="J11" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K11" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001533359890056984</v>
+        <v>0.002753413961155804</v>
       </c>
       <c r="M11" t="n">
-        <v>3.690621734219656</v>
+        <v>3.698609209284603</v>
       </c>
       <c r="N11" t="n">
-        <v>23.86012409656509</v>
+        <v>23.92877464156463</v>
       </c>
       <c r="O11" t="n">
-        <v>4.884682599367649</v>
+        <v>4.891704676446099</v>
       </c>
       <c r="P11" t="n">
-        <v>282.2704779467465</v>
+        <v>282.1838142009917</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33325,28 +33553,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01247082581654893</v>
+        <v>0.01841659308040373</v>
       </c>
       <c r="J12" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K12" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003305911007637219</v>
+        <v>0.0007307540645321575</v>
       </c>
       <c r="M12" t="n">
-        <v>3.930394974798144</v>
+        <v>3.926723667490034</v>
       </c>
       <c r="N12" t="n">
-        <v>26.34111942836019</v>
+        <v>26.26507267509785</v>
       </c>
       <c r="O12" t="n">
-        <v>5.132360025208694</v>
+        <v>5.124946114360409</v>
       </c>
       <c r="P12" t="n">
-        <v>311.7835459097388</v>
+        <v>311.7232607218023</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33403,28 +33631,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06559674291458779</v>
+        <v>-0.05534303353591038</v>
       </c>
       <c r="J13" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K13" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00934387474869447</v>
+        <v>0.006704112931691264</v>
       </c>
       <c r="M13" t="n">
-        <v>3.887172632530468</v>
+        <v>3.901609617932442</v>
       </c>
       <c r="N13" t="n">
-        <v>25.5528313957924</v>
+        <v>25.69874867501212</v>
       </c>
       <c r="O13" t="n">
-        <v>5.054980850190473</v>
+        <v>5.069393324157449</v>
       </c>
       <c r="P13" t="n">
-        <v>301.5582873604699</v>
+        <v>301.454319624336</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33481,28 +33709,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1574910003910416</v>
+        <v>-0.1485912901053364</v>
       </c>
       <c r="J14" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K14" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06441395145802875</v>
+        <v>0.0580680015363787</v>
       </c>
       <c r="M14" t="n">
-        <v>3.642695665749634</v>
+        <v>3.654720996757444</v>
       </c>
       <c r="N14" t="n">
-        <v>20.17873028744796</v>
+        <v>20.28234276697038</v>
       </c>
       <c r="O14" t="n">
-        <v>4.492074163173173</v>
+        <v>4.503592207002137</v>
       </c>
       <c r="P14" t="n">
-        <v>297.9148039626023</v>
+        <v>297.8245655851109</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33559,28 +33787,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2887021375176742</v>
+        <v>-0.278120650055817</v>
       </c>
       <c r="J15" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K15" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2087793878369502</v>
+        <v>0.1964726350167816</v>
       </c>
       <c r="M15" t="n">
-        <v>3.262305806996274</v>
+        <v>3.282619963904813</v>
       </c>
       <c r="N15" t="n">
-        <v>17.73198334520122</v>
+        <v>17.95437644492949</v>
       </c>
       <c r="O15" t="n">
-        <v>4.210936160190656</v>
+        <v>4.237260488208094</v>
       </c>
       <c r="P15" t="n">
-        <v>308.8700645535818</v>
+        <v>308.7628486225983</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33637,28 +33865,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3850683594105731</v>
+        <v>-0.3744425644801774</v>
       </c>
       <c r="J16" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K16" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3237134657777233</v>
+        <v>0.3111445826056358</v>
       </c>
       <c r="M16" t="n">
-        <v>3.311527551211566</v>
+        <v>3.335140672463587</v>
       </c>
       <c r="N16" t="n">
-        <v>17.38973593335824</v>
+        <v>17.61738760582353</v>
       </c>
       <c r="O16" t="n">
-        <v>4.170100230612957</v>
+        <v>4.197307185068009</v>
       </c>
       <c r="P16" t="n">
-        <v>315.6239879206174</v>
+        <v>315.5163262713414</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33715,28 +33943,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3785794086956714</v>
+        <v>-0.3720501940467014</v>
       </c>
       <c r="J17" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K17" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3074701826698543</v>
+        <v>0.3023745293738653</v>
       </c>
       <c r="M17" t="n">
-        <v>3.437208783875583</v>
+        <v>3.439082547183687</v>
       </c>
       <c r="N17" t="n">
-        <v>18.08123143582584</v>
+        <v>18.08543395827238</v>
       </c>
       <c r="O17" t="n">
-        <v>4.252203127300699</v>
+        <v>4.2526972568327</v>
       </c>
       <c r="P17" t="n">
-        <v>310.8421913257245</v>
+        <v>310.7759842445678</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33793,28 +34021,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2996656531832488</v>
+        <v>-0.2945690160602735</v>
       </c>
       <c r="J18" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K18" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2519748284210925</v>
+        <v>0.2479187170375812</v>
       </c>
       <c r="M18" t="n">
-        <v>2.964126079036582</v>
+        <v>2.967166372328085</v>
       </c>
       <c r="N18" t="n">
-        <v>14.9317787969914</v>
+        <v>14.90659091344901</v>
       </c>
       <c r="O18" t="n">
-        <v>3.86416598983421</v>
+        <v>3.86090545253947</v>
       </c>
       <c r="P18" t="n">
-        <v>318.0373931643669</v>
+        <v>317.9857151535229</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33871,28 +34099,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2558490416658883</v>
+        <v>-0.2540412995167171</v>
       </c>
       <c r="J19" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K19" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2495469316777561</v>
+        <v>0.2500886062165866</v>
       </c>
       <c r="M19" t="n">
-        <v>2.593425472601349</v>
+        <v>2.583029916427666</v>
       </c>
       <c r="N19" t="n">
-        <v>11.02598631907057</v>
+        <v>10.95906335115897</v>
       </c>
       <c r="O19" t="n">
-        <v>3.320540064367628</v>
+        <v>3.310447605862231</v>
       </c>
       <c r="P19" t="n">
-        <v>320.0699030126253</v>
+        <v>320.0515770116764</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33930,7 +34158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T420"/>
+  <dimension ref="A1:T423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76705,6 +76933,312 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-38.52837499273442,178.28915318169268</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-38.52863671262545,178.28827513505473</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-38.52899809739754,178.2874967507714</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-38.52940712263793,178.28676600633335</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-38.52986612168217,178.2860852342924</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-38.530350438453574,178.28534428783377</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-38.530877800377944,178.28453001402198</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-38.53147052587248,178.28387944025295</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-38.53209470584816,178.28345642575462</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-38.532776968618926,178.28314268403207</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-38.533547027505435,178.28281228569267</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-38.53430294536615,178.2825086231527</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-38.53499131640802,178.28227777470616</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-38.53568747331029,178.2822221688053</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-38.53637252645391,178.2820984337612</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-38.5370425938007,178.28181991233552</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>-38.53774208168446,178.28172011215972</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>-38.538430565866,178.2815429478247</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:35+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-38.528360077924965,178.28913826766873</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-38.52863544026441,178.2882738627731</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-38.52899703709137,178.2874956905379</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-38.52940330551852,178.28676218949195</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-38.52986082010639,178.28607993311516</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-38.530343956861905,178.2853368637451</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-38.53087252984959,178.2845217536768</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-38.53146508499198,178.28386920512472</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-38.53209062517439,178.28344874934882</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-38.53277313983357,178.28313548141136</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-38.533544711180284,178.2828047148147</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-38.534301903085705,178.28249910247598</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-38.53499037335547,178.28226858330666</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-38.53568642550849,178.28221299572306</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-38.53637166472934,178.28209200358793</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-38.53704163334637,178.2818131556137</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>-38.53774227377493,178.28172146351747</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>-38.53842954138018,178.28153574051385</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:10+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-38.528343820073104,178.28912201068303</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-38.52863091631393,178.28826933910548</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-38.528993856172804,178.28749250983762</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-38.52939362134453,178.2867525060259</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-38.52984922732635,178.28606834121035</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-38.53033045911247,178.28532140327613</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-38.53087094302373,178.28451926669143</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-38.531464833099335,178.28386873127621</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-38.53209112896131,178.2834496970532</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-38.53276240915618,178.28311529512303</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-38.533543177837984,178.28279970310695</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-38.53430143157762,178.28249479550325</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>-38.53498995422078,178.2822644982403</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-38.53568736982373,178.28222126282185</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>-38.53637128677985,178.28208918333652</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>-38.537042769883946,178.28182115106785</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>-38.537741281307355,178.28171448150252</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>-38.5384288530535,178.28153089810192</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T423"/>
+  <dimension ref="A1:T424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28348,6 +28348,72 @@
       <c r="T423" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>281.18</v>
+      </c>
+      <c r="C424" t="n">
+        <v>263.44</v>
+      </c>
+      <c r="D424" t="n">
+        <v>255.7</v>
+      </c>
+      <c r="E424" t="n">
+        <v>253.11</v>
+      </c>
+      <c r="F424" t="n">
+        <v>258.66</v>
+      </c>
+      <c r="G424" t="n">
+        <v>262.11</v>
+      </c>
+      <c r="H424" t="n">
+        <v>256.89</v>
+      </c>
+      <c r="I424" t="n">
+        <v>251.91</v>
+      </c>
+      <c r="J424" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="K424" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="L424" t="n">
+        <v>315.24</v>
+      </c>
+      <c r="M424" t="n">
+        <v>304.23</v>
+      </c>
+      <c r="N424" t="n">
+        <v>298.46</v>
+      </c>
+      <c r="O424" t="n">
+        <v>309.15</v>
+      </c>
+      <c r="P424" t="n">
+        <v>311.38</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>305.07</v>
+      </c>
+      <c r="R424" t="n">
+        <v>311.89</v>
+      </c>
+      <c r="S424" t="n">
+        <v>314.08</v>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28362,7 +28428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32605,6 +32671,16 @@
       </c>
       <c r="B424" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -32773,28 +32849,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2958425923004635</v>
+        <v>-0.2961177091472136</v>
       </c>
       <c r="J2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04188434402996755</v>
+        <v>0.04220082668620817</v>
       </c>
       <c r="M2" t="n">
-        <v>8.337527008082668</v>
+        <v>8.318995329746082</v>
       </c>
       <c r="N2" t="n">
-        <v>113.1999844127553</v>
+        <v>112.9305304341088</v>
       </c>
       <c r="O2" t="n">
-        <v>10.63954813010192</v>
+        <v>10.62687773685709</v>
       </c>
       <c r="P2" t="n">
-        <v>289.6860687938174</v>
+        <v>289.6888799049301</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32851,28 +32927,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3786457727757333</v>
+        <v>-0.3774269023935194</v>
       </c>
       <c r="J3" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09226740386922161</v>
+        <v>0.0922155759449601</v>
       </c>
       <c r="M3" t="n">
-        <v>7.044702834800264</v>
+        <v>7.033537888682804</v>
       </c>
       <c r="N3" t="n">
-        <v>79.75071863319511</v>
+        <v>79.57437865611844</v>
       </c>
       <c r="O3" t="n">
-        <v>8.930325785389641</v>
+        <v>8.920447222876129</v>
       </c>
       <c r="P3" t="n">
-        <v>271.1958236107764</v>
+        <v>271.1833693386487</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32929,28 +33005,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2160508685657465</v>
+        <v>-0.2152393575823401</v>
       </c>
       <c r="J4" t="n">
+        <v>423</v>
+      </c>
+      <c r="K4" t="n">
         <v>422</v>
       </c>
-      <c r="K4" t="n">
-        <v>421</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0388988486675137</v>
+        <v>0.03883896096532946</v>
       </c>
       <c r="M4" t="n">
-        <v>6.630518289198887</v>
+        <v>6.618341557937462</v>
       </c>
       <c r="N4" t="n">
-        <v>64.85817092680431</v>
+        <v>64.71063601869284</v>
       </c>
       <c r="O4" t="n">
-        <v>8.053457079217862</v>
+        <v>8.044292139069343</v>
       </c>
       <c r="P4" t="n">
-        <v>259.8922989462425</v>
+        <v>259.8839979737564</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33007,28 +33083,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.258051630276898</v>
+        <v>-0.2592320140212328</v>
       </c>
       <c r="J5" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K5" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05441637662721133</v>
+        <v>0.05518942561024709</v>
       </c>
       <c r="M5" t="n">
-        <v>6.583295170534783</v>
+        <v>6.573458650479388</v>
       </c>
       <c r="N5" t="n">
-        <v>65.528809216358</v>
+        <v>65.38705831907994</v>
       </c>
       <c r="O5" t="n">
-        <v>8.09498667178384</v>
+        <v>8.086226457321112</v>
       </c>
       <c r="P5" t="n">
-        <v>262.4212213184962</v>
+        <v>262.4332313964696</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33085,28 +33161,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1225058306619242</v>
+        <v>-0.1230504714697241</v>
       </c>
       <c r="J6" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01442318510644625</v>
+        <v>0.014635237515915</v>
       </c>
       <c r="M6" t="n">
-        <v>6.082064960705901</v>
+        <v>6.070482939504807</v>
       </c>
       <c r="N6" t="n">
-        <v>58.46363791698776</v>
+        <v>58.32726515752636</v>
       </c>
       <c r="O6" t="n">
-        <v>7.646151837165395</v>
+        <v>7.637228892571334</v>
       </c>
       <c r="P6" t="n">
-        <v>263.0527334504507</v>
+        <v>263.0582623753978</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33163,28 +33239,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02452499650361923</v>
+        <v>0.02435664739214102</v>
       </c>
       <c r="J7" t="n">
+        <v>423</v>
+      </c>
+      <c r="K7" t="n">
         <v>422</v>
       </c>
-      <c r="K7" t="n">
-        <v>421</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0005467457489795047</v>
+        <v>0.0005425074263221141</v>
       </c>
       <c r="M7" t="n">
-        <v>6.452023069409544</v>
+        <v>6.437553502720976</v>
       </c>
       <c r="N7" t="n">
-        <v>62.40224766537934</v>
+        <v>62.25464355969218</v>
       </c>
       <c r="O7" t="n">
-        <v>7.899509330672339</v>
+        <v>7.890161187180664</v>
       </c>
       <c r="P7" t="n">
-        <v>261.7847576530264</v>
+        <v>261.786469295474</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33241,28 +33317,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05591023981390594</v>
+        <v>0.05586107385836443</v>
       </c>
       <c r="J8" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K8" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004137987697133139</v>
+        <v>0.004155487848335526</v>
       </c>
       <c r="M8" t="n">
-        <v>5.343529203025587</v>
+        <v>5.331123147227419</v>
       </c>
       <c r="N8" t="n">
-        <v>42.60312158101435</v>
+        <v>42.50242781939174</v>
       </c>
       <c r="O8" t="n">
-        <v>6.527106677618679</v>
+        <v>6.519388607790744</v>
       </c>
       <c r="P8" t="n">
-        <v>255.481265043639</v>
+        <v>255.481765293632</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33319,28 +33395,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0869185734164062</v>
+        <v>0.08652935185181314</v>
       </c>
       <c r="J9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01513528308537915</v>
+        <v>0.01509018667411699</v>
       </c>
       <c r="M9" t="n">
-        <v>4.399140837061529</v>
+        <v>4.390360799550359</v>
       </c>
       <c r="N9" t="n">
-        <v>27.83940508176076</v>
+        <v>27.77502215090953</v>
       </c>
       <c r="O9" t="n">
-        <v>5.276306007213831</v>
+        <v>5.270201338744995</v>
       </c>
       <c r="P9" t="n">
-        <v>250.3571701486619</v>
+        <v>250.3611303703797</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33397,28 +33473,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09444373922536745</v>
+        <v>0.09406311369300203</v>
       </c>
       <c r="J10" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K10" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02060905217901177</v>
+        <v>0.02056598364445017</v>
       </c>
       <c r="M10" t="n">
-        <v>3.984198502331735</v>
+        <v>3.9767347487639</v>
       </c>
       <c r="N10" t="n">
-        <v>24.00452705767179</v>
+        <v>23.94914751087891</v>
       </c>
       <c r="O10" t="n">
-        <v>4.899441504668852</v>
+        <v>4.893786622941269</v>
       </c>
       <c r="P10" t="n">
-        <v>263.3247848489445</v>
+        <v>263.3286576084131</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33475,28 +33551,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03408091030295499</v>
+        <v>0.0354245756406428</v>
       </c>
       <c r="J11" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K11" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002753413961155804</v>
+        <v>0.00298982033065609</v>
       </c>
       <c r="M11" t="n">
-        <v>3.698609209284603</v>
+        <v>3.69522976805588</v>
       </c>
       <c r="N11" t="n">
-        <v>23.92877464156463</v>
+        <v>23.88909069028561</v>
       </c>
       <c r="O11" t="n">
-        <v>4.891704676446099</v>
+        <v>4.887646743606335</v>
       </c>
       <c r="P11" t="n">
-        <v>282.1838142009917</v>
+        <v>282.1701631294953</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33553,28 +33629,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01841659308040373</v>
+        <v>0.01992166649751272</v>
       </c>
       <c r="J12" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K12" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0007307540645321575</v>
+        <v>0.0008594059144820809</v>
       </c>
       <c r="M12" t="n">
-        <v>3.926723667490034</v>
+        <v>3.923741821872003</v>
       </c>
       <c r="N12" t="n">
-        <v>26.26507267509785</v>
+        <v>26.22438168593537</v>
       </c>
       <c r="O12" t="n">
-        <v>5.124946114360409</v>
+        <v>5.120974681243344</v>
       </c>
       <c r="P12" t="n">
-        <v>311.7232607218023</v>
+        <v>311.7079470162537</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33631,28 +33707,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.05534303353591038</v>
+        <v>-0.05321931249547768</v>
       </c>
       <c r="J13" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K13" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006704112931691264</v>
+        <v>0.006229383413850487</v>
       </c>
       <c r="M13" t="n">
-        <v>3.901609617932442</v>
+        <v>3.901522630448735</v>
       </c>
       <c r="N13" t="n">
-        <v>25.69874867501212</v>
+        <v>25.68060609730979</v>
       </c>
       <c r="O13" t="n">
-        <v>5.069393324157449</v>
+        <v>5.067603585257019</v>
       </c>
       <c r="P13" t="n">
-        <v>301.454319624336</v>
+        <v>301.4327113504068</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33709,28 +33785,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1485912901053364</v>
+        <v>-0.1462816268931473</v>
       </c>
       <c r="J14" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K14" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0580680015363787</v>
+        <v>0.05656485650477128</v>
       </c>
       <c r="M14" t="n">
-        <v>3.654720996757444</v>
+        <v>3.656057062588316</v>
       </c>
       <c r="N14" t="n">
-        <v>20.28234276697038</v>
+        <v>20.28479317818402</v>
       </c>
       <c r="O14" t="n">
-        <v>4.503592207002137</v>
+        <v>4.503864249528845</v>
       </c>
       <c r="P14" t="n">
-        <v>297.8245655851109</v>
+        <v>297.8010654010363</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33787,28 +33863,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.278120650055817</v>
+        <v>-0.274204175921864</v>
       </c>
       <c r="J15" t="n">
+        <v>423</v>
+      </c>
+      <c r="K15" t="n">
         <v>422</v>
       </c>
-      <c r="K15" t="n">
-        <v>421</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1964726350167816</v>
+        <v>0.1917097471286903</v>
       </c>
       <c r="M15" t="n">
-        <v>3.282619963904813</v>
+        <v>3.290988368875268</v>
       </c>
       <c r="N15" t="n">
-        <v>17.95437644492949</v>
+        <v>18.0571567804247</v>
       </c>
       <c r="O15" t="n">
-        <v>4.237260488208094</v>
+        <v>4.249371339436541</v>
       </c>
       <c r="P15" t="n">
-        <v>308.7628486225983</v>
+        <v>308.7230289685828</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33865,28 +33941,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3744425644801774</v>
+        <v>-0.3714863780050494</v>
       </c>
       <c r="J16" t="n">
+        <v>423</v>
+      </c>
+      <c r="K16" t="n">
         <v>422</v>
       </c>
-      <c r="K16" t="n">
-        <v>421</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.3111445826056358</v>
+        <v>0.3080328716634252</v>
       </c>
       <c r="M16" t="n">
-        <v>3.335140672463587</v>
+        <v>3.340595681826664</v>
       </c>
       <c r="N16" t="n">
-        <v>17.61738760582353</v>
+        <v>17.65843773672437</v>
       </c>
       <c r="O16" t="n">
-        <v>4.197307185068009</v>
+        <v>4.20219439539919</v>
       </c>
       <c r="P16" t="n">
-        <v>315.5163262713414</v>
+        <v>315.486270073185</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33943,28 +34019,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3720501940467014</v>
+        <v>-0.369906246139607</v>
       </c>
       <c r="J17" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K17" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3023745293738653</v>
+        <v>0.3006971117868871</v>
       </c>
       <c r="M17" t="n">
-        <v>3.439082547183687</v>
+        <v>3.439563201409619</v>
       </c>
       <c r="N17" t="n">
-        <v>18.08543395827238</v>
+        <v>18.08610530145473</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2526972568327</v>
+        <v>4.252776187557338</v>
       </c>
       <c r="P17" t="n">
-        <v>310.7759842445678</v>
+        <v>310.7541701678673</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34021,28 +34097,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2945690160602735</v>
+        <v>-0.2936583173037217</v>
       </c>
       <c r="J18" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K18" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2479187170375812</v>
+        <v>0.2477841693663151</v>
       </c>
       <c r="M18" t="n">
-        <v>2.967166372328085</v>
+        <v>2.964455968759361</v>
       </c>
       <c r="N18" t="n">
-        <v>14.90659091344901</v>
+        <v>14.87918641188375</v>
       </c>
       <c r="O18" t="n">
-        <v>3.86090545253947</v>
+        <v>3.857354846508647</v>
       </c>
       <c r="P18" t="n">
-        <v>317.9857151535229</v>
+        <v>317.9764490456755</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34099,28 +34175,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2540412995167171</v>
+        <v>-0.2536122617173663</v>
       </c>
       <c r="J19" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K19" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2500886062165866</v>
+        <v>0.2505499200959285</v>
       </c>
       <c r="M19" t="n">
-        <v>2.583029916427666</v>
+        <v>2.578852484368301</v>
       </c>
       <c r="N19" t="n">
-        <v>10.95906335115897</v>
+        <v>10.93489447190512</v>
       </c>
       <c r="O19" t="n">
-        <v>3.310447605862231</v>
+        <v>3.306795196546819</v>
       </c>
       <c r="P19" t="n">
-        <v>320.0515770116764</v>
+        <v>320.0472116707876</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34158,7 +34234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T423"/>
+  <dimension ref="A1:T424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77239,6 +77315,108 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-38.528343820073104,178.28912201068303</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-38.52863091631393,178.28826933910548</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-38.52898869601579,178.2874873500355</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-38.52938287685832,178.28674176232946</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-38.52983459497387,178.28605370997013</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-38.53030680463471,178.28529430920102</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-38.53084991757519,178.284486314145</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-38.531452792628585,178.28384608132203</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-38.532085637683466,178.28343936707614</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-38.532756313323596,178.28310382779753</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-38.53354219910874,178.28279650414467</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-38.534299086442864,178.28247337398156</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>-38.53498917416414,178.28225689547796</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-38.53568831413836,178.28222952992087</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>-38.536370273874866,178.2820816250629</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>-38.53704235368716,178.28181822315503</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>-38.537739440438926,178.28170153099126</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>-38.538429109175084,178.2815326999296</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
